--- a/gold.xlsx
+++ b/gold.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emiratessteeluae-my.sharepoint.com/personal/shakeel_awan_emsteel_com/Documents/1. Shakeel/Personel/BANK/GOLD XAU account/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="783" documentId="13_ncr:1_{851D1004-1C5D-48B9-BE48-07C0F232C6FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{641A42F2-2E37-4408-96C1-DB50CDC40B7A}"/>
+  <xr:revisionPtr revIDLastSave="799" documentId="13_ncr:1_{851D1004-1C5D-48B9-BE48-07C0F232C6FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B5AD685-ECBC-46B8-93A5-F7FAE7C57C26}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="67">
   <si>
     <t>XAU account</t>
   </si>
@@ -456,7 +456,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -642,6 +642,45 @@
     </xf>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1195,7 +1234,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDAADDF0-12CA-41AA-907F-C3C1F5BA90E3}">
-  <dimension ref="A1:AD40"/>
+  <dimension ref="A1:AD45"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -2897,14 +2936,14 @@
       <c r="B29" s="52"/>
       <c r="C29" s="24"/>
       <c r="D29" s="5">
-        <f t="shared" ref="D29:D36" si="22">D28+C29</f>
+        <f t="shared" ref="D29:D37" si="22">D28+C29</f>
         <v>64683.9</v>
       </c>
       <c r="E29" s="22">
         <v>69716.61</v>
       </c>
       <c r="F29" s="17">
-        <f t="shared" ref="F29:F36" si="23">E29-D29</f>
+        <f t="shared" ref="F29:F37" si="23">E29-D29</f>
         <v>5032.7099999999991</v>
       </c>
       <c r="G29" s="19">
@@ -2938,11 +2977,11 @@
       </c>
       <c r="O29" s="47"/>
       <c r="P29" s="26">
-        <f t="shared" ref="P29:P36" si="28">N29-K29</f>
+        <f t="shared" ref="P29:P37" si="28">N29-K29</f>
         <v>-3.6659486223129534E-2</v>
       </c>
       <c r="Q29" s="1">
-        <f t="shared" ref="Q29:Q36" si="29">N29-L29</f>
+        <f t="shared" ref="Q29:Q37" si="29">N29-L29</f>
         <v>23.64186766549858</v>
       </c>
       <c r="R29" s="1"/>
@@ -2974,7 +3013,7 @@
         <v>16931.170989999999</v>
       </c>
       <c r="J30" s="19">
-        <f t="shared" ref="J30:J36" si="30">H30-I30</f>
+        <f t="shared" ref="J30:J37" si="30">H30-I30</f>
         <v>736.4732299999996</v>
       </c>
       <c r="K30" s="27">
@@ -2986,7 +3025,7 @@
         <v>544.35813233450142</v>
       </c>
       <c r="M30" s="15">
-        <f t="shared" ref="M30:M36" si="33">K30-L30</f>
+        <f t="shared" ref="M30:M37" si="33">K30-L30</f>
         <v>23.67852715172171</v>
       </c>
       <c r="N30" s="1">
@@ -3033,11 +3072,11 @@
         <v>1000</v>
       </c>
       <c r="K31" s="27">
-        <f t="shared" ref="K31:K36" si="34">H31/31.103</f>
+        <f t="shared" ref="K31:K37" si="34">H31/31.103</f>
         <v>594.79792946018063</v>
       </c>
       <c r="L31" s="27">
-        <f t="shared" ref="L31:L36" si="35">I31/31.103</f>
+        <f t="shared" ref="L31:L37" si="35">I31/31.103</f>
         <v>562.64669002990058</v>
       </c>
       <c r="M31" s="15">
@@ -3340,69 +3379,204 @@
       </c>
       <c r="R36" s="1"/>
     </row>
-    <row r="37" spans="1:19" ht="23.25" x14ac:dyDescent="0.2">
-      <c r="C37" s="54"/>
-    </row>
-    <row r="38" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="54" t="s">
+    <row r="37" spans="1:19" ht="15" x14ac:dyDescent="0.2">
+      <c r="A37" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" s="52"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="5">
+        <f t="shared" si="22"/>
+        <v>64683.9</v>
+      </c>
+      <c r="E37" s="22">
+        <f>4.03*I37</f>
+        <v>78321.643771800009</v>
+      </c>
+      <c r="F37" s="17">
+        <f t="shared" si="23"/>
+        <v>13637.743771800007</v>
+      </c>
+      <c r="G37" s="19"/>
+      <c r="H37" s="29">
+        <v>20158.342250000002</v>
+      </c>
+      <c r="I37" s="28">
+        <v>19434.65106</v>
+      </c>
+      <c r="J37" s="19">
+        <f t="shared" si="30"/>
+        <v>723.69119000000137</v>
+      </c>
+      <c r="K37" s="27">
+        <f t="shared" si="34"/>
+        <v>648.11568819728006</v>
+      </c>
+      <c r="L37" s="27">
+        <f t="shared" si="35"/>
+        <v>624.84811947400567</v>
+      </c>
+      <c r="M37" s="15">
+        <f t="shared" si="33"/>
+        <v>23.267568723274394</v>
+      </c>
+      <c r="N37" s="1">
+        <v>650</v>
+      </c>
+      <c r="O37" s="47"/>
+      <c r="P37" s="26">
+        <f t="shared" si="28"/>
+        <v>1.8843118027199353</v>
+      </c>
+      <c r="Q37" s="1">
+        <f t="shared" si="29"/>
+        <v>25.151880525994329</v>
+      </c>
+      <c r="R37" s="1"/>
+    </row>
+    <row r="38" spans="1:19" ht="15" x14ac:dyDescent="0.2">
+      <c r="A38" s="62"/>
+      <c r="B38" s="63"/>
+      <c r="C38" s="64"/>
+      <c r="D38" s="65"/>
+      <c r="E38" s="66"/>
+      <c r="F38" s="67"/>
+      <c r="G38" s="67"/>
+      <c r="H38" s="68"/>
+      <c r="I38" s="69"/>
+      <c r="J38" s="67"/>
+      <c r="K38" s="70"/>
+      <c r="L38" s="70"/>
+      <c r="M38" s="71"/>
+      <c r="N38" s="72"/>
+      <c r="O38" s="73"/>
+      <c r="P38" s="74"/>
+      <c r="Q38" s="72"/>
+      <c r="R38" s="72"/>
+    </row>
+    <row r="39" spans="1:19" ht="15" x14ac:dyDescent="0.2">
+      <c r="A39" s="62"/>
+      <c r="B39" s="63"/>
+      <c r="C39" s="64"/>
+      <c r="D39" s="65"/>
+      <c r="E39" s="66"/>
+      <c r="F39" s="67"/>
+      <c r="G39" s="67"/>
+      <c r="H39" s="68"/>
+      <c r="I39" s="69"/>
+      <c r="J39" s="67"/>
+      <c r="K39" s="70"/>
+      <c r="L39" s="70"/>
+      <c r="M39" s="71"/>
+      <c r="N39" s="72"/>
+      <c r="O39" s="73"/>
+      <c r="P39" s="74"/>
+      <c r="Q39" s="72"/>
+      <c r="R39" s="72"/>
+    </row>
+    <row r="40" spans="1:19" ht="15" x14ac:dyDescent="0.2">
+      <c r="A40" s="62"/>
+      <c r="B40" s="63"/>
+      <c r="C40" s="64"/>
+      <c r="D40" s="65"/>
+      <c r="E40" s="66"/>
+      <c r="F40" s="67"/>
+      <c r="G40" s="67"/>
+      <c r="H40" s="68"/>
+      <c r="I40" s="69"/>
+      <c r="J40" s="67"/>
+      <c r="K40" s="70"/>
+      <c r="L40" s="70"/>
+      <c r="M40" s="71"/>
+      <c r="N40" s="72"/>
+      <c r="O40" s="73"/>
+      <c r="P40" s="74"/>
+      <c r="Q40" s="72"/>
+      <c r="R40" s="72"/>
+    </row>
+    <row r="41" spans="1:19" ht="15" x14ac:dyDescent="0.2">
+      <c r="A41" s="62"/>
+      <c r="B41" s="63"/>
+      <c r="C41" s="64"/>
+      <c r="D41" s="65"/>
+      <c r="E41" s="66"/>
+      <c r="F41" s="67"/>
+      <c r="G41" s="67"/>
+      <c r="H41" s="68"/>
+      <c r="I41" s="69"/>
+      <c r="J41" s="67"/>
+      <c r="K41" s="70"/>
+      <c r="L41" s="70"/>
+      <c r="M41" s="71"/>
+      <c r="N41" s="72"/>
+      <c r="O41" s="73"/>
+      <c r="P41" s="74"/>
+      <c r="Q41" s="72"/>
+      <c r="R41" s="72"/>
+    </row>
+    <row r="42" spans="1:19" ht="23.25" x14ac:dyDescent="0.2">
+      <c r="C42" s="54"/>
+    </row>
+    <row r="43" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="C38" s="54" t="s">
+      <c r="C43" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="D38" s="53"/>
-      <c r="E38" s="53"/>
-      <c r="F38" s="53">
-        <f>H38*4</f>
+      <c r="D43" s="53"/>
+      <c r="E43" s="53"/>
+      <c r="F43" s="53">
+        <f>H43*4</f>
         <v>72521.475040000005</v>
       </c>
-      <c r="G38" s="53">
-        <f>I38*4</f>
+      <c r="G43" s="53">
+        <f>I43*4</f>
         <v>77112.871960000004</v>
       </c>
-      <c r="H38" s="58">
+      <c r="H43" s="58">
         <v>18130.368760000001</v>
       </c>
-      <c r="I38">
+      <c r="I43">
         <v>19278.217990000001</v>
       </c>
-      <c r="J38">
+      <c r="J43">
         <v>727521.48</v>
       </c>
     </row>
-    <row r="39" spans="1:19" ht="23.25" x14ac:dyDescent="0.2">
-      <c r="A39" s="53"/>
-      <c r="B39" s="54" t="s">
+    <row r="44" spans="1:19" ht="23.25" x14ac:dyDescent="0.2">
+      <c r="A44" s="53"/>
+      <c r="B44" s="54" t="s">
         <v>51</v>
       </c>
-      <c r="C39" s="54">
+      <c r="C44" s="54">
         <f>I22*4</f>
         <v>72697.809880000001</v>
       </c>
-      <c r="D39" s="54" t="s">
+      <c r="D44" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="E39" s="53"/>
-      <c r="F39" s="55"/>
-      <c r="I39">
+      <c r="E44" s="53"/>
+      <c r="F44" s="55"/>
+      <c r="I44">
         <f>I36*4</f>
         <v>74604.506800000003</v>
       </c>
     </row>
-    <row r="40" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="54" t="s">
+    <row r="45" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B45" s="54" t="s">
         <v>50</v>
       </c>
-      <c r="C40" s="54">
-        <f>C39-D23</f>
+      <c r="C45" s="54">
+        <f>C44-D23</f>
         <v>8013.9098799999992</v>
       </c>
-      <c r="D40" s="54" t="s">
+      <c r="D45" s="54" t="s">
         <v>52</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F27:F36">
+  <conditionalFormatting sqref="F27:F41">
     <cfRule type="cellIs" dxfId="19" priority="6" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -3436,7 +3610,7 @@
       <formula>"D11&lt;D12"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G28:G36">
+  <conditionalFormatting sqref="G28:G41">
     <cfRule type="cellIs" dxfId="9" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>

--- a/gold.xlsx
+++ b/gold.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emiratessteeluae-my.sharepoint.com/personal/shakeel_awan_emsteel_com/Documents/1. Shakeel/Personel/BANK/GOLD XAU account/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="799" documentId="13_ncr:1_{851D1004-1C5D-48B9-BE48-07C0F232C6FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B5AD685-ECBC-46B8-93A5-F7FAE7C57C26}"/>
+  <xr:revisionPtr revIDLastSave="800" documentId="13_ncr:1_{851D1004-1C5D-48B9-BE48-07C0F232C6FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{590A1431-195C-4E95-A1B8-F1B2F8E2DDFD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="68">
   <si>
     <t>XAU account</t>
   </si>
@@ -240,6 +240,9 @@
   </si>
   <si>
     <t>27.02.2026</t>
+  </si>
+  <si>
+    <t>02.03.2026</t>
   </si>
 </sst>
 </file>
@@ -634,6 +637,45 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -642,45 +684,6 @@
     </xf>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3381,7 +3384,7 @@
     </row>
     <row r="37" spans="1:19" ht="15" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B37" s="52"/>
       <c r="C37" s="24"/>
@@ -3435,84 +3438,84 @@
       <c r="R37" s="1"/>
     </row>
     <row r="38" spans="1:19" ht="15" x14ac:dyDescent="0.2">
-      <c r="A38" s="62"/>
-      <c r="B38" s="63"/>
-      <c r="C38" s="64"/>
-      <c r="D38" s="65"/>
-      <c r="E38" s="66"/>
-      <c r="F38" s="67"/>
-      <c r="G38" s="67"/>
-      <c r="H38" s="68"/>
-      <c r="I38" s="69"/>
-      <c r="J38" s="67"/>
-      <c r="K38" s="70"/>
-      <c r="L38" s="70"/>
-      <c r="M38" s="71"/>
-      <c r="N38" s="72"/>
-      <c r="O38" s="73"/>
-      <c r="P38" s="74"/>
-      <c r="Q38" s="72"/>
-      <c r="R38" s="72"/>
+      <c r="A38" s="59"/>
+      <c r="B38" s="60"/>
+      <c r="C38" s="61"/>
+      <c r="D38" s="62"/>
+      <c r="E38" s="63"/>
+      <c r="F38" s="64"/>
+      <c r="G38" s="64"/>
+      <c r="H38" s="65"/>
+      <c r="I38" s="66"/>
+      <c r="J38" s="64"/>
+      <c r="K38" s="67"/>
+      <c r="L38" s="67"/>
+      <c r="M38" s="68"/>
+      <c r="N38" s="69"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="69"/>
+      <c r="R38" s="69"/>
     </row>
     <row r="39" spans="1:19" ht="15" x14ac:dyDescent="0.2">
-      <c r="A39" s="62"/>
-      <c r="B39" s="63"/>
-      <c r="C39" s="64"/>
-      <c r="D39" s="65"/>
-      <c r="E39" s="66"/>
-      <c r="F39" s="67"/>
-      <c r="G39" s="67"/>
-      <c r="H39" s="68"/>
-      <c r="I39" s="69"/>
-      <c r="J39" s="67"/>
-      <c r="K39" s="70"/>
-      <c r="L39" s="70"/>
-      <c r="M39" s="71"/>
-      <c r="N39" s="72"/>
-      <c r="O39" s="73"/>
-      <c r="P39" s="74"/>
-      <c r="Q39" s="72"/>
-      <c r="R39" s="72"/>
+      <c r="A39" s="59"/>
+      <c r="B39" s="60"/>
+      <c r="C39" s="61"/>
+      <c r="D39" s="62"/>
+      <c r="E39" s="63"/>
+      <c r="F39" s="64"/>
+      <c r="G39" s="64"/>
+      <c r="H39" s="65"/>
+      <c r="I39" s="66"/>
+      <c r="J39" s="64"/>
+      <c r="K39" s="67"/>
+      <c r="L39" s="67"/>
+      <c r="M39" s="68"/>
+      <c r="N39" s="69"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="69"/>
+      <c r="R39" s="69"/>
     </row>
     <row r="40" spans="1:19" ht="15" x14ac:dyDescent="0.2">
-      <c r="A40" s="62"/>
-      <c r="B40" s="63"/>
-      <c r="C40" s="64"/>
-      <c r="D40" s="65"/>
-      <c r="E40" s="66"/>
-      <c r="F40" s="67"/>
-      <c r="G40" s="67"/>
-      <c r="H40" s="68"/>
-      <c r="I40" s="69"/>
-      <c r="J40" s="67"/>
-      <c r="K40" s="70"/>
-      <c r="L40" s="70"/>
-      <c r="M40" s="71"/>
-      <c r="N40" s="72"/>
-      <c r="O40" s="73"/>
-      <c r="P40" s="74"/>
-      <c r="Q40" s="72"/>
-      <c r="R40" s="72"/>
+      <c r="A40" s="59"/>
+      <c r="B40" s="60"/>
+      <c r="C40" s="61"/>
+      <c r="D40" s="62"/>
+      <c r="E40" s="63"/>
+      <c r="F40" s="64"/>
+      <c r="G40" s="64"/>
+      <c r="H40" s="65"/>
+      <c r="I40" s="66"/>
+      <c r="J40" s="64"/>
+      <c r="K40" s="67"/>
+      <c r="L40" s="67"/>
+      <c r="M40" s="68"/>
+      <c r="N40" s="69"/>
+      <c r="O40" s="70"/>
+      <c r="P40" s="71"/>
+      <c r="Q40" s="69"/>
+      <c r="R40" s="69"/>
     </row>
     <row r="41" spans="1:19" ht="15" x14ac:dyDescent="0.2">
-      <c r="A41" s="62"/>
-      <c r="B41" s="63"/>
-      <c r="C41" s="64"/>
-      <c r="D41" s="65"/>
-      <c r="E41" s="66"/>
-      <c r="F41" s="67"/>
-      <c r="G41" s="67"/>
-      <c r="H41" s="68"/>
-      <c r="I41" s="69"/>
-      <c r="J41" s="67"/>
-      <c r="K41" s="70"/>
-      <c r="L41" s="70"/>
-      <c r="M41" s="71"/>
-      <c r="N41" s="72"/>
-      <c r="O41" s="73"/>
-      <c r="P41" s="74"/>
-      <c r="Q41" s="72"/>
-      <c r="R41" s="72"/>
+      <c r="A41" s="59"/>
+      <c r="B41" s="60"/>
+      <c r="C41" s="61"/>
+      <c r="D41" s="62"/>
+      <c r="E41" s="63"/>
+      <c r="F41" s="64"/>
+      <c r="G41" s="64"/>
+      <c r="H41" s="65"/>
+      <c r="I41" s="66"/>
+      <c r="J41" s="64"/>
+      <c r="K41" s="67"/>
+      <c r="L41" s="67"/>
+      <c r="M41" s="68"/>
+      <c r="N41" s="69"/>
+      <c r="O41" s="70"/>
+      <c r="P41" s="71"/>
+      <c r="Q41" s="69"/>
+      <c r="R41" s="69"/>
     </row>
     <row r="42" spans="1:19" ht="23.25" x14ac:dyDescent="0.2">
       <c r="C42" s="54"/>
@@ -3813,10 +3816,10 @@
       <c r="G7" s="40"/>
       <c r="H7" s="40"/>
       <c r="I7" s="40"/>
-      <c r="J7" s="61" t="s">
+      <c r="J7" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="K7" s="61"/>
+      <c r="K7" s="74"/>
       <c r="L7" s="40"/>
       <c r="M7" s="40"/>
       <c r="N7" s="40"/>
@@ -5146,8 +5149,8 @@
       <c r="A32" s="3"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
-      <c r="D32" s="59"/>
-      <c r="E32" s="60"/>
+      <c r="D32" s="72"/>
+      <c r="E32" s="73"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
@@ -5168,8 +5171,8 @@
       <c r="A33" s="3"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="59"/>
-      <c r="E33" s="60"/>
+      <c r="D33" s="72"/>
+      <c r="E33" s="73"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
@@ -5190,8 +5193,8 @@
       <c r="A34" s="3"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
-      <c r="D34" s="59"/>
-      <c r="E34" s="60"/>
+      <c r="D34" s="72"/>
+      <c r="E34" s="73"/>
       <c r="F34" s="46"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
@@ -5212,8 +5215,8 @@
       <c r="A35" s="3"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
-      <c r="D35" s="59"/>
-      <c r="E35" s="60"/>
+      <c r="D35" s="72"/>
+      <c r="E35" s="73"/>
       <c r="F35" s="2"/>
       <c r="G35" s="29"/>
       <c r="H35" s="29"/>

--- a/gold.xlsx
+++ b/gold.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emiratessteeluae-my.sharepoint.com/personal/shakeel_awan_emsteel_com/Documents/1. Shakeel/Personel/BANK/GOLD XAU account/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="800" documentId="13_ncr:1_{851D1004-1C5D-48B9-BE48-07C0F232C6FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{590A1431-195C-4E95-A1B8-F1B2F8E2DDFD}"/>
+  <xr:revisionPtr revIDLastSave="844" documentId="13_ncr:1_{851D1004-1C5D-48B9-BE48-07C0F232C6FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35C2D0A6-7E5B-4C0B-95A9-D8E7CAD1B8E5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="3" r:id="rId1"/>
     <sheet name="Table 1 (2)" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="70">
   <si>
     <t>XAU account</t>
   </si>
@@ -243,6 +244,12 @@
   </si>
   <si>
     <t>02.03.2026</t>
+  </si>
+  <si>
+    <t>08.03.2026</t>
+  </si>
+  <si>
+    <t>14.03.2026</t>
   </si>
 </sst>
 </file>
@@ -1237,7 +1244,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDAADDF0-12CA-41AA-907F-C3C1F5BA90E3}">
-  <dimension ref="A1:AD45"/>
+  <dimension ref="A1:AD46"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -1407,8 +1414,8 @@
         <v>13407.35</v>
       </c>
       <c r="F3" s="17">
-        <f>E3-D3</f>
-        <v>-150.96999999999935</v>
+        <f t="shared" ref="F3:F9" si="1">(I3*1)-D3</f>
+        <v>-391.75362999999925</v>
       </c>
       <c r="G3" s="17"/>
       <c r="H3" s="28">
@@ -1418,15 +1425,15 @@
         <v>13166.56637</v>
       </c>
       <c r="J3" s="19">
-        <f t="shared" ref="J3:J24" si="1">H3-I3</f>
+        <f t="shared" ref="J3:J24" si="2">H3-I3</f>
         <v>481.56703000000016</v>
       </c>
       <c r="K3" s="27">
-        <f t="shared" ref="K3:K9" si="2">H3/31.1</f>
+        <f t="shared" ref="K3:K9" si="3">H3/31.1</f>
         <v>438.84673311897109</v>
       </c>
       <c r="L3" s="27">
-        <f t="shared" ref="L3:L10" si="3">I3/31.103</f>
+        <f t="shared" ref="L3:L10" si="4">I3/31.103</f>
         <v>423.32142783654308</v>
       </c>
       <c r="M3" s="15">
@@ -1442,7 +1449,7 @@
         <v>1.6532668810289124</v>
       </c>
       <c r="Q3" s="30">
-        <f t="shared" ref="Q3:Q20" si="4">N3-L3</f>
+        <f t="shared" ref="Q3:Q20" si="5">N3-L3</f>
         <v>17.17857216345692</v>
       </c>
       <c r="R3" s="1"/>
@@ -1476,8 +1483,8 @@
         <v>13392.92</v>
       </c>
       <c r="F4" s="17">
-        <f t="shared" ref="F4:F22" si="5">E4-D4</f>
-        <v>-165.39999999999964</v>
+        <f t="shared" si="1"/>
+        <v>-391.75362999999925</v>
       </c>
       <c r="G4" s="17"/>
       <c r="H4" s="28">
@@ -1487,15 +1494,15 @@
         <v>13166.56637</v>
       </c>
       <c r="J4" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>481.56703000000016</v>
       </c>
       <c r="K4" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>438.84673311897109</v>
       </c>
       <c r="L4" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>423.32142783654308</v>
       </c>
       <c r="M4" s="15">
@@ -1511,7 +1518,7 @@
         <v>1.1532668810289124</v>
       </c>
       <c r="Q4" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>16.67857216345692</v>
       </c>
       <c r="R4" s="1"/>
@@ -1533,8 +1540,8 @@
         <v>13344.36</v>
       </c>
       <c r="F5" s="17">
-        <f t="shared" si="5"/>
-        <v>-213.95999999999913</v>
+        <f t="shared" si="1"/>
+        <v>-391.75362999999925</v>
       </c>
       <c r="G5" s="17"/>
       <c r="H5" s="28">
@@ -1544,15 +1551,15 @@
         <v>13166.56637</v>
       </c>
       <c r="J5" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>481.56703000000016</v>
       </c>
       <c r="K5" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>438.84673311897109</v>
       </c>
       <c r="L5" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>423.32142783654308</v>
       </c>
       <c r="M5" s="15">
@@ -1568,7 +1575,7 @@
         <v>-1.3467331189710876</v>
       </c>
       <c r="Q5" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>14.17857216345692</v>
       </c>
       <c r="R5" s="1"/>
@@ -1594,8 +1601,8 @@
         <v>13399.45</v>
       </c>
       <c r="F6" s="17">
-        <f t="shared" si="5"/>
-        <v>-158.86999999999898</v>
+        <f t="shared" si="1"/>
+        <v>-391.75362999999925</v>
       </c>
       <c r="G6" s="17"/>
       <c r="H6" s="28">
@@ -1605,15 +1612,15 @@
         <v>13166.56637</v>
       </c>
       <c r="J6" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>481.56703000000016</v>
       </c>
       <c r="K6" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>438.84673311897109</v>
       </c>
       <c r="L6" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>423.32142783654308</v>
       </c>
       <c r="M6" s="15">
@@ -1629,7 +1636,7 @@
         <v>1.1532668810289124</v>
       </c>
       <c r="Q6" s="30">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>16.67857216345692</v>
       </c>
       <c r="R6" s="1"/>
@@ -1655,8 +1662,8 @@
         <v>13828</v>
       </c>
       <c r="F7" s="17">
-        <f t="shared" si="5"/>
-        <v>269.68000000000029</v>
+        <f t="shared" si="1"/>
+        <v>29.833309999999983</v>
       </c>
       <c r="G7" s="17"/>
       <c r="H7" s="28">
@@ -1666,15 +1673,15 @@
         <v>13588.15331</v>
       </c>
       <c r="J7" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>480.4651300000005</v>
       </c>
       <c r="K7" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>452.36715241157555</v>
       </c>
       <c r="L7" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>436.87597048516216</v>
       </c>
       <c r="M7" s="15">
@@ -1690,7 +1697,7 @@
         <v>3.632847588424454</v>
       </c>
       <c r="Q7" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>19.124029514837844</v>
       </c>
       <c r="R7" s="1"/>
@@ -1716,8 +1723,8 @@
         <v>13792.87</v>
       </c>
       <c r="F8" s="17">
-        <f t="shared" si="5"/>
-        <v>234.55000000000109</v>
+        <f t="shared" si="1"/>
+        <v>-5.2071099999993748</v>
       </c>
       <c r="G8" s="17"/>
       <c r="H8" s="28">
@@ -1727,15 +1734,15 @@
         <v>13553.11289</v>
       </c>
       <c r="J8" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>479.51015000000007</v>
       </c>
       <c r="K8" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>451.20974405144693</v>
       </c>
       <c r="L8" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>435.7493775520046</v>
       </c>
       <c r="M8" s="15">
@@ -1751,7 +1758,7 @@
         <v>2.0402559485530674</v>
       </c>
       <c r="Q8" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>17.500622447995397</v>
       </c>
       <c r="R8" s="1"/>
@@ -1777,8 +1784,8 @@
         <v>14260.64</v>
       </c>
       <c r="F9" s="17">
-        <f t="shared" si="5"/>
-        <v>702.31999999999971</v>
+        <f t="shared" si="1"/>
+        <v>656.77768000000106</v>
       </c>
       <c r="G9" s="17"/>
       <c r="H9" s="28">
@@ -1788,15 +1795,15 @@
         <v>14215.097680000001</v>
       </c>
       <c r="J9" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>121.35591999999997</v>
       </c>
       <c r="K9" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>460.97921543408359</v>
       </c>
       <c r="L9" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>457.03300903449826</v>
       </c>
       <c r="M9" s="15">
@@ -1812,7 +1819,7 @@
         <v>6.270784565916415</v>
       </c>
       <c r="Q9" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.216990965501736</v>
       </c>
       <c r="R9" s="1"/>
@@ -1834,8 +1841,8 @@
         <v>14826.34</v>
       </c>
       <c r="F10" s="17">
-        <f t="shared" si="5"/>
-        <v>1268.0200000000004</v>
+        <f>(I10*1)-D10</f>
+        <v>1217.0938299999998</v>
       </c>
       <c r="G10" s="17"/>
       <c r="H10" s="28">
@@ -1845,7 +1852,7 @@
         <v>14775.41383</v>
       </c>
       <c r="J10" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>121.61303000000044</v>
       </c>
       <c r="K10" s="27">
@@ -1853,7 +1860,7 @@
         <v>478.95787737517281</v>
       </c>
       <c r="L10" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>475.04786772980094</v>
       </c>
       <c r="M10" s="15">
@@ -1869,7 +1876,7 @@
         <v>6.2921226248271864</v>
       </c>
       <c r="Q10" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.202132270199058</v>
       </c>
       <c r="R10" s="1"/>
@@ -1895,8 +1902,8 @@
         <v>29345.91</v>
       </c>
       <c r="F11" s="17">
-        <f t="shared" si="5"/>
-        <v>1054.0099999999984</v>
+        <f t="shared" ref="F11:F16" si="8">(I11*2)-D11</f>
+        <v>959.72508000000016</v>
       </c>
       <c r="G11" s="19"/>
       <c r="H11" s="29">
@@ -1906,7 +1913,7 @@
         <v>14625.812540000001</v>
       </c>
       <c r="J11" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>123.78009999999995</v>
       </c>
       <c r="K11" s="27">
@@ -1933,7 +1940,7 @@
         <v>7.2365710610932297</v>
       </c>
       <c r="Q11" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>11.216638585209012</v>
       </c>
       <c r="R11" s="1"/>
@@ -1955,8 +1962,8 @@
         <v>29909.200000000001</v>
       </c>
       <c r="F12" s="17">
-        <f t="shared" si="5"/>
-        <v>1617.2999999999993</v>
+        <f t="shared" si="8"/>
+        <v>1493.4854399999967</v>
       </c>
       <c r="G12" s="17"/>
       <c r="H12" s="28">
@@ -1966,15 +1973,15 @@
         <v>14892.692719999999</v>
       </c>
       <c r="J12" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>123.81683000000157</v>
       </c>
       <c r="K12" s="27">
-        <f t="shared" ref="K12:L19" si="8">H12/31.103</f>
+        <f t="shared" ref="K12:L19" si="9">H12/31.103</f>
         <v>482.79939394913674</v>
       </c>
       <c r="L12" s="27">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>478.8185294023084</v>
       </c>
       <c r="M12" s="15">
@@ -1990,7 +1997,7 @@
         <v>7.7006060508632572</v>
       </c>
       <c r="Q12" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>11.6814705976916</v>
       </c>
       <c r="R12" s="1"/>
@@ -2010,8 +2017,8 @@
         <v>31609.47</v>
       </c>
       <c r="F13" s="17">
-        <f t="shared" si="5"/>
-        <v>3317.5699999999997</v>
+        <f t="shared" si="8"/>
+        <v>2835.3792599999979</v>
       </c>
       <c r="G13" s="19"/>
       <c r="H13" s="29">
@@ -2021,15 +2028,15 @@
         <v>15563.63963</v>
       </c>
       <c r="J13" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>482.19144000000051</v>
       </c>
       <c r="K13" s="27">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>515.89335658939649</v>
       </c>
       <c r="L13" s="27">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>500.390304150725</v>
       </c>
       <c r="M13" s="15">
@@ -2045,7 +2052,7 @@
         <v>-3.6433565893964897</v>
       </c>
       <c r="Q13" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>11.859695849274999</v>
       </c>
       <c r="R13" s="1"/>
@@ -2067,8 +2074,8 @@
         <v>29205.71</v>
       </c>
       <c r="F14" s="17">
-        <f t="shared" si="5"/>
-        <v>913.80999999999767</v>
+        <f t="shared" si="8"/>
+        <v>431.91497999999774</v>
       </c>
       <c r="G14" s="19"/>
       <c r="H14" s="29">
@@ -2078,15 +2085,15 @@
         <v>14361.90749</v>
       </c>
       <c r="J14" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>481.89760000000024</v>
       </c>
       <c r="K14" s="27">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>477.2467315049995</v>
       </c>
       <c r="L14" s="27">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>461.75312638652218</v>
       </c>
       <c r="M14" s="15">
@@ -2102,7 +2109,7 @@
         <v>4.2532684950004978</v>
       </c>
       <c r="Q14" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>19.746873613477817</v>
       </c>
       <c r="R14" s="1"/>
@@ -2124,8 +2131,8 @@
         <v>33002.239999999998</v>
       </c>
       <c r="F15" s="17">
-        <f t="shared" si="5"/>
-        <v>4710.3399999999965</v>
+        <f t="shared" si="8"/>
+        <v>3777.5926399999989</v>
       </c>
       <c r="G15" s="19"/>
       <c r="H15" s="29">
@@ -2135,15 +2142,15 @@
         <v>16034.74632</v>
       </c>
       <c r="J15" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>932.74292999999852</v>
       </c>
       <c r="K15" s="27">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>545.52580940745258</v>
       </c>
       <c r="L15" s="27">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>515.53696813812167</v>
       </c>
       <c r="M15" s="15">
@@ -2157,7 +2164,7 @@
         <v>-545.52580940745258</v>
       </c>
       <c r="Q15" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-515.53696813812167</v>
       </c>
       <c r="R15" s="1"/>
@@ -2179,8 +2186,8 @@
         <v>33689.78</v>
       </c>
       <c r="F16" s="17">
-        <f t="shared" si="5"/>
-        <v>5397.8799999999974</v>
+        <f t="shared" si="8"/>
+        <v>5084.787639999995</v>
       </c>
       <c r="G16" s="19"/>
       <c r="H16" s="29">
@@ -2190,15 +2197,15 @@
         <v>16688.343819999998</v>
       </c>
       <c r="J16" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>313.0953300000001</v>
       </c>
       <c r="K16" s="27">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>546.61734077098663</v>
       </c>
       <c r="L16" s="27">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>536.55093785165411</v>
       </c>
       <c r="M16" s="15">
@@ -2214,7 +2221,7 @@
         <v>7.3826592290133704</v>
       </c>
       <c r="Q16" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>17.449062148345888</v>
       </c>
       <c r="R16" s="1"/>
@@ -2236,8 +2243,8 @@
         <v>33689.78</v>
       </c>
       <c r="F17" s="17">
-        <f t="shared" si="5"/>
-        <v>5397.8799999999974</v>
+        <f>(I17*2)-D17</f>
+        <v>4548.1880400000009</v>
       </c>
       <c r="G17" s="19"/>
       <c r="H17" s="29">
@@ -2247,15 +2254,15 @@
         <v>16420.044020000001</v>
       </c>
       <c r="J17" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>933.11022999999841</v>
       </c>
       <c r="K17" s="27">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>557.92541716233154</v>
       </c>
       <c r="L17" s="27">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>527.92476674275792</v>
       </c>
       <c r="M17" s="15">
@@ -2271,7 +2278,7 @@
         <v>-7.9254171623315415</v>
       </c>
       <c r="Q17" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>22.075233257242076</v>
       </c>
       <c r="R17" s="1"/>
@@ -2297,8 +2304,8 @@
         <v>51409.64</v>
       </c>
       <c r="F18" s="17">
-        <f t="shared" si="5"/>
-        <v>5831.739999999998</v>
+        <f t="shared" ref="F18:F20" si="10">(I18*3.03)-D18</f>
+        <v>5851.6528636999938</v>
       </c>
       <c r="G18" s="19"/>
       <c r="H18" s="29">
@@ -2308,15 +2315,15 @@
         <v>16973.449789999999</v>
       </c>
       <c r="J18" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>312.19986000000063</v>
       </c>
       <c r="K18" s="27">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>555.75506060508633</v>
       </c>
       <c r="L18" s="27">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>545.71744815612635</v>
       </c>
       <c r="M18" s="15">
@@ -2335,7 +2342,7 @@
         <v>6.244939394913672</v>
       </c>
       <c r="Q18" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>16.282551843873648</v>
       </c>
       <c r="R18" s="1"/>
@@ -2357,8 +2364,8 @@
         <v>53614.65</v>
       </c>
       <c r="F19" s="17">
-        <f t="shared" si="5"/>
-        <v>8036.75</v>
+        <f t="shared" si="10"/>
+        <v>8106.0928819999899</v>
       </c>
       <c r="G19" s="19"/>
       <c r="H19" s="29">
@@ -2368,15 +2375,15 @@
         <v>17717.489399999999</v>
       </c>
       <c r="J19" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>312.49370000000272</v>
       </c>
       <c r="K19" s="27">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>579.68630357200266</v>
       </c>
       <c r="L19" s="27">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>569.63924380284857</v>
       </c>
       <c r="M19" s="15">
@@ -2392,7 +2399,7 @@
         <v>6.5636964279973427</v>
       </c>
       <c r="Q19" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>16.610756197151431</v>
       </c>
       <c r="R19" s="1"/>
@@ -2414,8 +2421,8 @@
         <v>54468.4</v>
       </c>
       <c r="F20" s="17">
-        <f t="shared" si="5"/>
-        <v>8890.5</v>
+        <f t="shared" si="10"/>
+        <v>4979.6040469999934</v>
       </c>
       <c r="G20" s="19"/>
       <c r="H20" s="29">
@@ -2425,15 +2432,15 @@
         <v>16685.644899999999</v>
       </c>
       <c r="J20" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>932.45348999999987</v>
       </c>
       <c r="K20" s="27">
-        <f t="shared" ref="K20:L24" si="9">H20/31.103</f>
+        <f t="shared" ref="K20:L24" si="11">H20/31.103</f>
         <v>566.44369964312114</v>
       </c>
       <c r="L20" s="27">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>536.46416422853099</v>
       </c>
       <c r="M20" s="15">
@@ -2449,7 +2456,7 @@
         <v>14.056300356878864</v>
       </c>
       <c r="Q20" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>44.03583577146901</v>
       </c>
       <c r="R20" s="1"/>
@@ -2471,8 +2478,8 @@
         <v>54468.4</v>
       </c>
       <c r="F21" s="17">
-        <f t="shared" si="5"/>
-        <v>8890.5</v>
+        <f>(I21*3.03)-D21</f>
+        <v>8025.4218286999967</v>
       </c>
       <c r="G21" s="19"/>
       <c r="H21" s="29">
@@ -2482,15 +2489,15 @@
         <v>17690.865290000002</v>
       </c>
       <c r="J21" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>930.53912999999739</v>
       </c>
       <c r="K21" s="27">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>598.70123203549485</v>
       </c>
       <c r="L21" s="27">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>568.78324566762046</v>
       </c>
       <c r="M21" s="15">
@@ -2506,7 +2513,7 @@
         <v>2.2987679645051458</v>
       </c>
       <c r="Q21" s="16">
-        <f t="shared" ref="Q21:Q26" si="10">N21-L21</f>
+        <f t="shared" ref="Q21:Q26" si="12">N21-L21</f>
         <v>32.216754332379537</v>
       </c>
       <c r="R21" s="1"/>
@@ -2532,8 +2539,8 @@
         <v>74561.679999999993</v>
       </c>
       <c r="F22" s="17">
-        <f t="shared" si="5"/>
-        <v>9877.7799999999916</v>
+        <f t="shared" ref="F22:F31" si="13">(I22*4.03)-D22</f>
+        <v>8559.1434540999981</v>
       </c>
       <c r="G22" s="19">
         <f>I22*4</f>
@@ -2546,15 +2553,15 @@
         <v>18174.45247</v>
       </c>
       <c r="J22" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>931.93487000000096</v>
       </c>
       <c r="K22" s="27">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>614.29403401601132</v>
       </c>
       <c r="L22" s="27">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>584.33117287721439</v>
       </c>
       <c r="M22" s="15">
@@ -2573,7 +2580,7 @@
         <v>-4.2940340160113237</v>
       </c>
       <c r="Q22" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>25.668827122785615</v>
       </c>
       <c r="R22" s="1"/>
@@ -2595,8 +2602,8 @@
         <v>74736.37</v>
       </c>
       <c r="F23" s="17">
-        <f t="shared" ref="F23:F28" si="11">E23-D23</f>
-        <v>10052.469999999994</v>
+        <f t="shared" si="13"/>
+        <v>8734.2533618000089</v>
       </c>
       <c r="G23" s="19"/>
       <c r="H23" s="29">
@@ -2606,15 +2613,15 @@
         <v>18217.904060000001</v>
       </c>
       <c r="J23" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>932.37562999999864</v>
       </c>
       <c r="K23" s="27">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>615.70522747001894</v>
       </c>
       <c r="L23" s="27">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>585.72819535093072</v>
       </c>
       <c r="M23" s="15">
@@ -2630,7 +2637,7 @@
         <v>-2.70522747001894</v>
       </c>
       <c r="Q23" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>27.271804649069281</v>
       </c>
       <c r="R23" s="1"/>
@@ -2652,8 +2659,8 @@
         <v>77635.23</v>
       </c>
       <c r="F24" s="17">
-        <f t="shared" si="11"/>
-        <v>12951.329999999994</v>
+        <f t="shared" si="13"/>
+        <v>11214.307019699998</v>
       </c>
       <c r="G24" s="19"/>
       <c r="H24" s="29">
@@ -2663,15 +2670,15 @@
         <v>18833.30199</v>
       </c>
       <c r="J24" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1151.0091099999991</v>
       </c>
       <c r="K24" s="27">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>642.52037102530301</v>
       </c>
       <c r="L24" s="27">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>605.5140015432595</v>
       </c>
       <c r="M24" s="15">
@@ -2687,7 +2694,7 @@
         <v>-7.7703710253030067</v>
       </c>
       <c r="Q24" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>29.235998456740504</v>
       </c>
       <c r="R24" s="1"/>
@@ -2710,8 +2717,8 @@
         <v>78837.207999999999</v>
       </c>
       <c r="F25" s="17">
-        <f t="shared" si="11"/>
-        <v>14153.307999999997</v>
+        <f t="shared" si="13"/>
+        <v>14744.587059999998</v>
       </c>
       <c r="G25" s="19">
         <f>I25*4</f>
@@ -2724,15 +2731,15 @@
         <v>19709.302</v>
       </c>
       <c r="J25" s="19">
-        <f t="shared" ref="J25:J26" si="12">H25-I25</f>
+        <f t="shared" ref="J25:J26" si="14">H25-I25</f>
         <v>1129.7134000000005</v>
       </c>
       <c r="K25" s="27">
-        <f t="shared" ref="K25:K26" si="13">H25/31.103</f>
+        <f t="shared" ref="K25:K26" si="15">H25/31.103</f>
         <v>670.0001736166929</v>
       </c>
       <c r="L25" s="27">
-        <f t="shared" ref="L25:L26" si="14">I25/31.103</f>
+        <f t="shared" ref="L25:L26" si="16">I25/31.103</f>
         <v>633.67848760569711</v>
       </c>
       <c r="M25" s="15">
@@ -2744,11 +2751,11 @@
       </c>
       <c r="O25" s="44"/>
       <c r="P25" s="26">
-        <f t="shared" ref="P25:P26" si="15">N25-K25</f>
+        <f t="shared" ref="P25:P26" si="17">N25-K25</f>
         <v>-6.0001736166929049</v>
       </c>
       <c r="Q25" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>30.321512394302886</v>
       </c>
       <c r="R25" s="1"/>
@@ -2770,8 +2777,8 @@
         <v>75378.3</v>
       </c>
       <c r="F26" s="17">
-        <f t="shared" si="11"/>
-        <v>10694.400000000001</v>
+        <f t="shared" si="13"/>
+        <v>8381.4861028000087</v>
       </c>
       <c r="G26" s="19">
         <f>I26*4</f>
@@ -2784,15 +2791,15 @@
         <v>18130.368760000001</v>
       </c>
       <c r="J26" s="19">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1147.8492299999998</v>
       </c>
       <c r="K26" s="27">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>619.81860238562194</v>
       </c>
       <c r="L26" s="27">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>582.91382696202936</v>
       </c>
       <c r="M26" s="15">
@@ -2804,11 +2811,11 @@
       </c>
       <c r="O26" s="44"/>
       <c r="P26" s="26">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>-17.818602385621944</v>
       </c>
       <c r="Q26" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>19.086173037970639</v>
       </c>
       <c r="R26" s="1"/>
@@ -2830,8 +2837,8 @@
         <v>75378.3</v>
       </c>
       <c r="F27" s="17">
-        <f t="shared" si="11"/>
-        <v>10694.400000000001</v>
+        <f t="shared" si="13"/>
+        <v>-203.89999999999418</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="29">
@@ -2841,19 +2848,19 @@
         <v>16000</v>
       </c>
       <c r="J27" s="19">
-        <f t="shared" ref="J27:J28" si="16">H27-I27</f>
+        <f t="shared" ref="J27:J28" si="18">H27-I27</f>
         <v>3278.217990000001</v>
       </c>
       <c r="K27" s="27">
-        <f t="shared" ref="K27:K28" si="17">H27/31.103</f>
+        <f t="shared" ref="K27:K28" si="19">H27/31.103</f>
         <v>619.81860238562194</v>
       </c>
       <c r="L27" s="27">
-        <f t="shared" ref="L27:L28" si="18">I27/31.103</f>
+        <f t="shared" ref="L27:L28" si="20">I27/31.103</f>
         <v>514.41983088448058</v>
       </c>
       <c r="M27" s="15">
-        <f t="shared" ref="M27:M28" si="19">K27-L27</f>
+        <f t="shared" ref="M27:M28" si="21">K27-L27</f>
         <v>105.39877150114137</v>
       </c>
       <c r="N27" s="1">
@@ -2861,11 +2868,11 @@
       </c>
       <c r="O27" s="48"/>
       <c r="P27" s="26">
-        <f t="shared" ref="P27:P28" si="20">N27-K27</f>
+        <f t="shared" ref="P27:P28" si="22">N27-K27</f>
         <v>-30.318602385621944</v>
       </c>
       <c r="Q27" s="1">
-        <f t="shared" ref="Q27:Q28" si="21">N27-L27</f>
+        <f t="shared" ref="Q27:Q28" si="23">N27-L27</f>
         <v>75.080169115519425</v>
       </c>
       <c r="R27" s="1"/>
@@ -2887,8 +2894,8 @@
         <v>67505.320000000007</v>
       </c>
       <c r="F28" s="17">
-        <f t="shared" si="11"/>
-        <v>2821.4200000000055</v>
+        <f t="shared" si="13"/>
+        <v>1312.9920000000056</v>
       </c>
       <c r="G28" s="19">
         <f>I28*4</f>
@@ -2901,19 +2908,19 @@
         <v>16376.4</v>
       </c>
       <c r="J28" s="19">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>748.60000000000036</v>
       </c>
       <c r="K28" s="27">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>550.58997524354561</v>
       </c>
       <c r="L28" s="27">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>526.52155740603791</v>
       </c>
       <c r="M28" s="15">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>24.068417837507695</v>
       </c>
       <c r="N28" s="1">
@@ -2921,11 +2928,11 @@
       </c>
       <c r="O28" s="47"/>
       <c r="P28" s="26">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>6.1600247564543906</v>
       </c>
       <c r="Q28" s="1">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>30.228442593962086</v>
       </c>
       <c r="R28" s="1"/>
@@ -2939,15 +2946,15 @@
       <c r="B29" s="52"/>
       <c r="C29" s="24"/>
       <c r="D29" s="5">
-        <f t="shared" ref="D29:D37" si="22">D28+C29</f>
+        <f t="shared" ref="D29:D39" si="24">D28+C29</f>
         <v>64683.9</v>
       </c>
       <c r="E29" s="22">
         <v>69716.61</v>
       </c>
       <c r="F29" s="17">
-        <f t="shared" ref="F29:F37" si="23">E29-D29</f>
-        <v>5032.7099999999991</v>
+        <f t="shared" si="13"/>
+        <v>3548.7190897000037</v>
       </c>
       <c r="G29" s="19">
         <f>I29*4</f>
@@ -2960,19 +2967,19 @@
         <v>16931.170989999999</v>
       </c>
       <c r="J29" s="19">
-        <f t="shared" ref="J29" si="24">H29-I29</f>
+        <f t="shared" ref="J29" si="25">H29-I29</f>
         <v>736.4732299999996</v>
       </c>
       <c r="K29" s="27">
-        <f t="shared" ref="K29" si="25">H29/31.103</f>
+        <f t="shared" ref="K29" si="26">H29/31.103</f>
         <v>568.03665948622313</v>
       </c>
       <c r="L29" s="27">
-        <f t="shared" ref="L29" si="26">I29/31.103</f>
+        <f t="shared" ref="L29" si="27">I29/31.103</f>
         <v>544.35813233450142</v>
       </c>
       <c r="M29" s="15">
-        <f t="shared" ref="M29" si="27">K29-L29</f>
+        <f t="shared" ref="M29" si="28">K29-L29</f>
         <v>23.67852715172171</v>
       </c>
       <c r="N29" s="1">
@@ -2980,11 +2987,11 @@
       </c>
       <c r="O29" s="47"/>
       <c r="P29" s="26">
-        <f t="shared" ref="P29:P37" si="28">N29-K29</f>
+        <f t="shared" ref="P29:P39" si="29">N29-K29</f>
         <v>-3.6659486223129534E-2</v>
       </c>
       <c r="Q29" s="1">
-        <f t="shared" ref="Q29:Q37" si="29">N29-L29</f>
+        <f t="shared" ref="Q29:Q39" si="30">N29-L29</f>
         <v>23.64186766549858</v>
       </c>
       <c r="R29" s="1"/>
@@ -2998,15 +3005,15 @@
       <c r="B30" s="52"/>
       <c r="C30" s="24"/>
       <c r="D30" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>64683.9</v>
       </c>
       <c r="E30" s="22">
         <v>73010.55</v>
       </c>
       <c r="F30" s="17">
-        <f t="shared" si="23"/>
-        <v>8326.6500000000015</v>
+        <f t="shared" si="13"/>
+        <v>3548.7190897000037</v>
       </c>
       <c r="G30" s="19"/>
       <c r="H30" s="29">
@@ -3016,19 +3023,19 @@
         <v>16931.170989999999</v>
       </c>
       <c r="J30" s="19">
-        <f t="shared" ref="J30:J37" si="30">H30-I30</f>
+        <f t="shared" ref="J30:J39" si="31">H30-I30</f>
         <v>736.4732299999996</v>
       </c>
       <c r="K30" s="27">
-        <f t="shared" ref="K30" si="31">H30/31.103</f>
+        <f t="shared" ref="K30" si="32">H30/31.103</f>
         <v>568.03665948622313</v>
       </c>
       <c r="L30" s="27">
-        <f t="shared" ref="L30" si="32">I30/31.103</f>
+        <f t="shared" ref="L30" si="33">I30/31.103</f>
         <v>544.35813233450142</v>
       </c>
       <c r="M30" s="15">
-        <f t="shared" ref="M30:M37" si="33">K30-L30</f>
+        <f t="shared" ref="M30:M39" si="34">K30-L30</f>
         <v>23.67852715172171</v>
       </c>
       <c r="N30" s="1">
@@ -3036,11 +3043,11 @@
       </c>
       <c r="O30" s="47"/>
       <c r="P30" s="26">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>24.71334051377687</v>
       </c>
       <c r="Q30" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>48.39186766549858</v>
       </c>
       <c r="R30" s="1"/>
@@ -3053,15 +3060,15 @@
       <c r="B31" s="52"/>
       <c r="C31" s="24"/>
       <c r="D31" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>64683.9</v>
       </c>
       <c r="E31" s="22">
         <v>72215.240000000005</v>
       </c>
       <c r="F31" s="17">
-        <f t="shared" si="23"/>
-        <v>7531.3400000000038</v>
+        <f t="shared" si="13"/>
+        <v>5841.0999999999985</v>
       </c>
       <c r="G31" s="19"/>
       <c r="H31" s="29">
@@ -3071,19 +3078,19 @@
         <v>17500</v>
       </c>
       <c r="J31" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1000</v>
       </c>
       <c r="K31" s="27">
-        <f t="shared" ref="K31:K37" si="34">H31/31.103</f>
+        <f t="shared" ref="K31:K39" si="35">H31/31.103</f>
         <v>594.79792946018063</v>
       </c>
       <c r="L31" s="27">
-        <f t="shared" ref="L31:L37" si="35">I31/31.103</f>
+        <f t="shared" ref="L31:L39" si="36">I31/31.103</f>
         <v>562.64669002990058</v>
       </c>
       <c r="M31" s="15">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>32.151239430280043</v>
       </c>
       <c r="N31" s="1">
@@ -3091,11 +3098,11 @@
       </c>
       <c r="O31" s="47"/>
       <c r="P31" s="26">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-0.29792946018062594</v>
       </c>
       <c r="Q31" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>31.853309970099417</v>
       </c>
       <c r="R31" s="1"/>
@@ -3108,15 +3115,15 @@
       <c r="B32" s="52"/>
       <c r="C32" s="24"/>
       <c r="D32" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>64683.9</v>
       </c>
       <c r="E32" s="22">
         <v>74499.350000000006</v>
       </c>
       <c r="F32" s="17">
-        <f t="shared" si="23"/>
-        <v>9815.4500000000044</v>
+        <f t="shared" ref="F32:F39" si="37">(I32*4.03)-D32</f>
+        <v>8358.8387521000041</v>
       </c>
       <c r="G32" s="19"/>
       <c r="H32" s="29">
@@ -3126,19 +3133,19 @@
         <v>18124.749070000002</v>
       </c>
       <c r="J32" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>722.88312999999835</v>
       </c>
       <c r="K32" s="27">
+        <f t="shared" si="35"/>
+        <v>605.97473555605563</v>
+      </c>
+      <c r="L32" s="27">
+        <f t="shared" si="36"/>
+        <v>582.73314696331545</v>
+      </c>
+      <c r="M32" s="15">
         <f t="shared" si="34"/>
-        <v>605.97473555605563</v>
-      </c>
-      <c r="L32" s="27">
-        <f t="shared" si="35"/>
-        <v>582.73314696331545</v>
-      </c>
-      <c r="M32" s="15">
-        <f t="shared" si="33"/>
         <v>23.241588592740186</v>
       </c>
       <c r="N32" s="1">
@@ -3146,11 +3153,11 @@
       </c>
       <c r="O32" s="47"/>
       <c r="P32" s="26">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>2.5252644439443657</v>
       </c>
       <c r="Q32" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>25.766853036684552</v>
       </c>
       <c r="R32" s="1"/>
@@ -3163,15 +3170,15 @@
       <c r="B33" s="52"/>
       <c r="C33" s="24"/>
       <c r="D33" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>64683.9</v>
       </c>
       <c r="E33" s="22">
         <v>73758.53</v>
       </c>
       <c r="F33" s="17">
-        <f t="shared" si="23"/>
-        <v>9074.6299999999974</v>
+        <f t="shared" si="37"/>
+        <v>-7457.9000000000015</v>
       </c>
       <c r="G33" s="19">
         <f>I33*4</f>
@@ -3184,19 +3191,19 @@
         <v>14200</v>
       </c>
       <c r="J33" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>8000</v>
       </c>
       <c r="K33" s="27">
+        <f t="shared" si="35"/>
+        <v>713.75751535221684</v>
+      </c>
+      <c r="L33" s="27">
+        <f t="shared" si="36"/>
+        <v>456.5475999099765</v>
+      </c>
+      <c r="M33" s="15">
         <f t="shared" si="34"/>
-        <v>713.75751535221684</v>
-      </c>
-      <c r="L33" s="27">
-        <f t="shared" si="35"/>
-        <v>456.5475999099765</v>
-      </c>
-      <c r="M33" s="15">
-        <f t="shared" si="33"/>
         <v>257.20991544224034</v>
       </c>
       <c r="N33" s="1">
@@ -3204,11 +3211,11 @@
       </c>
       <c r="O33" s="47"/>
       <c r="P33" s="26">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-106.75751535221684</v>
       </c>
       <c r="Q33" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>150.4524000900235</v>
       </c>
       <c r="R33" s="1"/>
@@ -3221,15 +3228,15 @@
       <c r="B34" s="52"/>
       <c r="C34" s="24"/>
       <c r="D34" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>64683.9</v>
       </c>
       <c r="E34" s="22">
         <v>73689.37</v>
       </c>
       <c r="F34" s="17">
-        <f t="shared" si="23"/>
-        <v>9005.4699999999939</v>
+        <f t="shared" si="37"/>
+        <v>7891.5336138000057</v>
       </c>
       <c r="G34" s="19">
         <f>I34*4</f>
@@ -3242,19 +3249,19 @@
         <v>18008.792460000001</v>
       </c>
       <c r="J34" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>552.82322999999815</v>
       </c>
       <c r="K34" s="27">
+        <f t="shared" si="35"/>
+        <v>596.77895026203248</v>
+      </c>
+      <c r="L34" s="27">
+        <f t="shared" si="36"/>
+        <v>579.00499823168184</v>
+      </c>
+      <c r="M34" s="15">
         <f t="shared" si="34"/>
-        <v>596.77895026203248</v>
-      </c>
-      <c r="L34" s="27">
-        <f t="shared" si="35"/>
-        <v>579.00499823168184</v>
-      </c>
-      <c r="M34" s="15">
-        <f t="shared" si="33"/>
         <v>17.773952030350642</v>
       </c>
       <c r="N34" s="1">
@@ -3262,11 +3269,11 @@
       </c>
       <c r="O34" s="47"/>
       <c r="P34" s="26">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>7.2210497379675189</v>
       </c>
       <c r="Q34" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>24.995001768318161</v>
       </c>
       <c r="R34" s="1"/>
@@ -3278,15 +3285,15 @@
       <c r="B35" s="52"/>
       <c r="C35" s="24"/>
       <c r="D35" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>64683.9</v>
       </c>
       <c r="E35" s="22">
         <v>74499.350000000006</v>
       </c>
       <c r="F35" s="17">
-        <f t="shared" si="23"/>
-        <v>9815.4500000000044</v>
+        <f t="shared" si="37"/>
+        <v>-6833.25</v>
       </c>
       <c r="G35" s="19">
         <f>I35*4</f>
@@ -3299,19 +3306,19 @@
         <v>14355</v>
       </c>
       <c r="J35" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>8000</v>
       </c>
       <c r="K35" s="27">
+        <f t="shared" si="35"/>
+        <v>718.74095746391015</v>
+      </c>
+      <c r="L35" s="27">
+        <f t="shared" si="36"/>
+        <v>461.53104202166992</v>
+      </c>
+      <c r="M35" s="15">
         <f t="shared" si="34"/>
-        <v>718.74095746391015</v>
-      </c>
-      <c r="L35" s="27">
-        <f t="shared" si="35"/>
-        <v>461.53104202166992</v>
-      </c>
-      <c r="M35" s="15">
-        <f t="shared" si="33"/>
         <v>257.20991544224023</v>
       </c>
       <c r="N35" s="1">
@@ -3319,11 +3326,11 @@
       </c>
       <c r="O35" s="47"/>
       <c r="P35" s="26">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-103.74095746391015</v>
       </c>
       <c r="Q35" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>153.46895797833008</v>
       </c>
       <c r="R35" s="1"/>
@@ -3335,15 +3342,15 @@
       <c r="B36" s="52"/>
       <c r="C36" s="24"/>
       <c r="D36" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>64683.9</v>
       </c>
       <c r="E36" s="22">
         <v>76611.03</v>
       </c>
       <c r="F36" s="17">
-        <f t="shared" si="23"/>
-        <v>11927.129999999997</v>
+        <f t="shared" si="37"/>
+        <v>10480.140600999999</v>
       </c>
       <c r="G36" s="19"/>
       <c r="H36" s="29">
@@ -3353,19 +3360,19 @@
         <v>18651.126700000001</v>
       </c>
       <c r="J36" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>718.108229999998</v>
       </c>
       <c r="K36" s="27">
+        <f t="shared" si="35"/>
+        <v>622.74490981577333</v>
+      </c>
+      <c r="L36" s="27">
+        <f t="shared" si="36"/>
+        <v>599.65684017618878</v>
+      </c>
+      <c r="M36" s="15">
         <f t="shared" si="34"/>
-        <v>622.74490981577333</v>
-      </c>
-      <c r="L36" s="27">
-        <f t="shared" si="35"/>
-        <v>599.65684017618878</v>
-      </c>
-      <c r="M36" s="15">
-        <f t="shared" si="33"/>
         <v>23.088069639584546</v>
       </c>
       <c r="N36" s="1">
@@ -3373,11 +3380,11 @@
       </c>
       <c r="O36" s="47"/>
       <c r="P36" s="26">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>8.255090184226674</v>
       </c>
       <c r="Q36" s="1">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>31.34315982381122</v>
       </c>
       <c r="R36" s="1"/>
@@ -3389,15 +3396,14 @@
       <c r="B37" s="52"/>
       <c r="C37" s="24"/>
       <c r="D37" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>64683.9</v>
       </c>
       <c r="E37" s="22">
-        <f>4.03*I37</f>
-        <v>78321.643771800009</v>
+        <v>75268.789999999994</v>
       </c>
       <c r="F37" s="17">
-        <f t="shared" si="23"/>
+        <f t="shared" si="37"/>
         <v>13637.743771800007</v>
       </c>
       <c r="G37" s="19"/>
@@ -3408,19 +3414,19 @@
         <v>19434.65106</v>
       </c>
       <c r="J37" s="19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>723.69119000000137</v>
       </c>
       <c r="K37" s="27">
+        <f t="shared" si="35"/>
+        <v>648.11568819728006</v>
+      </c>
+      <c r="L37" s="27">
+        <f t="shared" si="36"/>
+        <v>624.84811947400567</v>
+      </c>
+      <c r="M37" s="15">
         <f t="shared" si="34"/>
-        <v>648.11568819728006</v>
-      </c>
-      <c r="L37" s="27">
-        <f t="shared" si="35"/>
-        <v>624.84811947400567</v>
-      </c>
-      <c r="M37" s="15">
-        <f t="shared" si="33"/>
         <v>23.267568723274394</v>
       </c>
       <c r="N37" s="1">
@@ -3428,54 +3434,125 @@
       </c>
       <c r="O37" s="47"/>
       <c r="P37" s="26">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1.8843118027199353</v>
       </c>
       <c r="Q37" s="1">
+        <f t="shared" si="30"/>
+        <v>25.151880525994329</v>
+      </c>
+      <c r="R37" s="1"/>
+    </row>
+    <row r="38" spans="1:19" ht="15" x14ac:dyDescent="0.2">
+      <c r="A38" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B38" s="52"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="5">
+        <f t="shared" si="24"/>
+        <v>64683.9</v>
+      </c>
+      <c r="E38" s="22">
+        <v>75268.789999999994</v>
+      </c>
+      <c r="F38" s="17">
+        <f t="shared" si="37"/>
+        <v>13637.743771800007</v>
+      </c>
+      <c r="G38" s="19"/>
+      <c r="H38" s="29">
+        <v>20158.342250000002</v>
+      </c>
+      <c r="I38" s="28">
+        <v>19434.65106</v>
+      </c>
+      <c r="J38" s="19">
+        <f t="shared" si="31"/>
+        <v>723.69119000000137</v>
+      </c>
+      <c r="K38" s="27">
+        <f t="shared" si="35"/>
+        <v>648.11568819728006</v>
+      </c>
+      <c r="L38" s="27">
+        <f t="shared" si="36"/>
+        <v>624.84811947400567</v>
+      </c>
+      <c r="M38" s="15">
+        <f t="shared" si="34"/>
+        <v>23.267568723274394</v>
+      </c>
+      <c r="N38" s="1">
+        <v>623.25</v>
+      </c>
+      <c r="O38" s="47"/>
+      <c r="P38" s="26">
         <f t="shared" si="29"/>
-        <v>25.151880525994329</v>
-      </c>
-      <c r="R37" s="1"/>
-    </row>
-    <row r="38" spans="1:19" ht="15" x14ac:dyDescent="0.2">
-      <c r="A38" s="59"/>
-      <c r="B38" s="60"/>
-      <c r="C38" s="61"/>
-      <c r="D38" s="62"/>
-      <c r="E38" s="63"/>
-      <c r="F38" s="64"/>
-      <c r="G38" s="64"/>
-      <c r="H38" s="65"/>
-      <c r="I38" s="66"/>
-      <c r="J38" s="64"/>
-      <c r="K38" s="67"/>
-      <c r="L38" s="67"/>
-      <c r="M38" s="68"/>
-      <c r="N38" s="69"/>
-      <c r="O38" s="70"/>
-      <c r="P38" s="71"/>
-      <c r="Q38" s="69"/>
-      <c r="R38" s="69"/>
+        <v>-24.865688197280065</v>
+      </c>
+      <c r="Q38" s="1">
+        <f t="shared" si="30"/>
+        <v>-1.5981194740056708</v>
+      </c>
+      <c r="R38" s="1"/>
     </row>
     <row r="39" spans="1:19" ht="15" x14ac:dyDescent="0.2">
-      <c r="A39" s="59"/>
-      <c r="B39" s="60"/>
-      <c r="C39" s="61"/>
-      <c r="D39" s="62"/>
-      <c r="E39" s="63"/>
-      <c r="F39" s="64"/>
-      <c r="G39" s="64"/>
-      <c r="H39" s="65"/>
-      <c r="I39" s="66"/>
-      <c r="J39" s="64"/>
-      <c r="K39" s="67"/>
-      <c r="L39" s="67"/>
-      <c r="M39" s="68"/>
-      <c r="N39" s="69"/>
-      <c r="O39" s="70"/>
-      <c r="P39" s="71"/>
-      <c r="Q39" s="69"/>
-      <c r="R39" s="69"/>
+      <c r="A39" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B39" s="52"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="5">
+        <f t="shared" si="24"/>
+        <v>64683.9</v>
+      </c>
+      <c r="E39" s="22">
+        <v>75397.320000000007</v>
+      </c>
+      <c r="F39" s="17">
+        <f t="shared" si="37"/>
+        <v>9042.4038863000096</v>
+      </c>
+      <c r="G39" s="19">
+        <f>I39*4</f>
+        <v>73177.472840000002</v>
+      </c>
+      <c r="H39" s="29">
+        <v>19766.6168</v>
+      </c>
+      <c r="I39" s="28">
+        <v>18294.368210000001</v>
+      </c>
+      <c r="J39" s="19">
+        <f t="shared" si="31"/>
+        <v>1472.2485899999992</v>
+      </c>
+      <c r="K39" s="27">
+        <f t="shared" si="35"/>
+        <v>635.5212294633958</v>
+      </c>
+      <c r="L39" s="27">
+        <f t="shared" si="36"/>
+        <v>588.1866125454136</v>
+      </c>
+      <c r="M39" s="15">
+        <f t="shared" si="34"/>
+        <v>47.334616917982203</v>
+      </c>
+      <c r="N39" s="1">
+        <v>604</v>
+      </c>
+      <c r="O39" s="47"/>
+      <c r="P39" s="26">
+        <f t="shared" si="29"/>
+        <v>-31.521229463395798</v>
+      </c>
+      <c r="Q39" s="1">
+        <f t="shared" si="30"/>
+        <v>15.813387454586405</v>
+      </c>
+      <c r="R39" s="1"/>
     </row>
     <row r="40" spans="1:19" ht="15" x14ac:dyDescent="0.2">
       <c r="A40" s="59"/>
@@ -3506,7 +3583,10 @@
       <c r="F41" s="64"/>
       <c r="G41" s="64"/>
       <c r="H41" s="65"/>
-      <c r="I41" s="66"/>
+      <c r="I41" s="66">
+        <f>I38*4.03</f>
+        <v>78321.643771800009</v>
+      </c>
       <c r="J41" s="64"/>
       <c r="K41" s="67"/>
       <c r="L41" s="67"/>
@@ -3517,69 +3597,89 @@
       <c r="Q41" s="69"/>
       <c r="R41" s="69"/>
     </row>
-    <row r="42" spans="1:19" ht="23.25" x14ac:dyDescent="0.2">
-      <c r="C42" s="54"/>
-    </row>
-    <row r="43" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="54" t="s">
+    <row r="42" spans="1:19" ht="15" x14ac:dyDescent="0.2">
+      <c r="A42" s="59"/>
+      <c r="B42" s="60"/>
+      <c r="C42" s="61"/>
+      <c r="D42" s="62"/>
+      <c r="E42" s="63"/>
+      <c r="F42" s="64"/>
+      <c r="G42" s="64"/>
+      <c r="H42" s="65"/>
+      <c r="I42" s="66"/>
+      <c r="J42" s="64"/>
+      <c r="K42" s="67"/>
+      <c r="L42" s="67"/>
+      <c r="M42" s="68"/>
+      <c r="N42" s="69"/>
+      <c r="O42" s="70"/>
+      <c r="P42" s="71"/>
+      <c r="Q42" s="69"/>
+      <c r="R42" s="69"/>
+    </row>
+    <row r="43" spans="1:19" ht="23.25" x14ac:dyDescent="0.2">
+      <c r="C43" s="54"/>
+    </row>
+    <row r="44" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="C43" s="54" t="s">
+      <c r="C44" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="D43" s="53"/>
-      <c r="E43" s="53"/>
-      <c r="F43" s="53">
-        <f>H43*4</f>
+      <c r="D44" s="53"/>
+      <c r="E44" s="53"/>
+      <c r="F44" s="53">
+        <f>H44*4</f>
         <v>72521.475040000005</v>
       </c>
-      <c r="G43" s="53">
-        <f>I43*4</f>
+      <c r="G44" s="53">
+        <f>I44*4</f>
         <v>77112.871960000004</v>
       </c>
-      <c r="H43" s="58">
+      <c r="H44" s="58">
         <v>18130.368760000001</v>
       </c>
-      <c r="I43">
+      <c r="I44">
         <v>19278.217990000001</v>
       </c>
-      <c r="J43">
+      <c r="J44">
         <v>727521.48</v>
       </c>
     </row>
-    <row r="44" spans="1:19" ht="23.25" x14ac:dyDescent="0.2">
-      <c r="A44" s="53"/>
-      <c r="B44" s="54" t="s">
+    <row r="45" spans="1:19" ht="23.25" x14ac:dyDescent="0.2">
+      <c r="A45" s="53"/>
+      <c r="B45" s="54" t="s">
         <v>51</v>
       </c>
-      <c r="C44" s="54">
+      <c r="C45" s="54">
         <f>I22*4</f>
         <v>72697.809880000001</v>
       </c>
-      <c r="D44" s="54" t="s">
+      <c r="D45" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="E44" s="53"/>
-      <c r="F44" s="55"/>
-      <c r="I44">
+      <c r="E45" s="53"/>
+      <c r="F45" s="55"/>
+      <c r="I45">
         <f>I36*4</f>
         <v>74604.506800000003</v>
       </c>
     </row>
-    <row r="45" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B45" s="54" t="s">
+    <row r="46" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B46" s="54" t="s">
         <v>50</v>
       </c>
-      <c r="C45" s="54">
-        <f>C44-D23</f>
+      <c r="C46" s="54">
+        <f>C45-D23</f>
         <v>8013.9098799999992</v>
       </c>
-      <c r="D45" s="54" t="s">
+      <c r="D46" s="54" t="s">
         <v>52</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F27:F41">
+  <conditionalFormatting sqref="F3:F42">
     <cfRule type="cellIs" dxfId="19" priority="6" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -3596,7 +3696,7 @@
       <formula>"D11&lt;D12"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:G26">
+  <conditionalFormatting sqref="F2:G2 G3:G26">
     <cfRule type="cellIs" dxfId="14" priority="11" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -3613,7 +3713,7 @@
       <formula>"D11&lt;D12"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G28:G41">
+  <conditionalFormatting sqref="G28:G42">
     <cfRule type="cellIs" dxfId="9" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -5331,6 +5431,41 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C7F4534-1A00-44C5-937A-3E7E5546F7B2}">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1">
+        <v>76261.37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>75268.789999999994</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>800115.02</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>30002.32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>10000.39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="e558cee3-a297-449c-b5c0-354695d37a90" origin="userSelected"/>
 </file>

--- a/gold.xlsx
+++ b/gold.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emiratessteeluae-my.sharepoint.com/personal/shakeel_awan_emsteel_com/Documents/1. Shakeel/Personel/BANK/GOLD XAU account/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="844" documentId="13_ncr:1_{851D1004-1C5D-48B9-BE48-07C0F232C6FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35C2D0A6-7E5B-4C0B-95A9-D8E7CAD1B8E5}"/>
+  <xr:revisionPtr revIDLastSave="858" documentId="13_ncr:1_{851D1004-1C5D-48B9-BE48-07C0F232C6FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89465B88-AA25-48FE-81F6-C28DA2140968}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="71">
   <si>
     <t>XAU account</t>
   </si>
@@ -250,6 +250,9 @@
   </si>
   <si>
     <t>14.03.2026</t>
+  </si>
+  <si>
+    <t>21.03.2026</t>
   </si>
 </sst>
 </file>
@@ -2946,7 +2949,7 @@
       <c r="B29" s="52"/>
       <c r="C29" s="24"/>
       <c r="D29" s="5">
-        <f t="shared" ref="D29:D39" si="24">D28+C29</f>
+        <f t="shared" ref="D29:D40" si="24">D28+C29</f>
         <v>64683.9</v>
       </c>
       <c r="E29" s="22">
@@ -2987,11 +2990,11 @@
       </c>
       <c r="O29" s="47"/>
       <c r="P29" s="26">
-        <f t="shared" ref="P29:P39" si="29">N29-K29</f>
+        <f t="shared" ref="P29:P40" si="29">N29-K29</f>
         <v>-3.6659486223129534E-2</v>
       </c>
       <c r="Q29" s="1">
-        <f t="shared" ref="Q29:Q39" si="30">N29-L29</f>
+        <f t="shared" ref="Q29:Q40" si="30">N29-L29</f>
         <v>23.64186766549858</v>
       </c>
       <c r="R29" s="1"/>
@@ -3023,7 +3026,7 @@
         <v>16931.170989999999</v>
       </c>
       <c r="J30" s="19">
-        <f t="shared" ref="J30:J39" si="31">H30-I30</f>
+        <f t="shared" ref="J30:J40" si="31">H30-I30</f>
         <v>736.4732299999996</v>
       </c>
       <c r="K30" s="27">
@@ -3035,7 +3038,7 @@
         <v>544.35813233450142</v>
       </c>
       <c r="M30" s="15">
-        <f t="shared" ref="M30:M39" si="34">K30-L30</f>
+        <f t="shared" ref="M30:M40" si="34">K30-L30</f>
         <v>23.67852715172171</v>
       </c>
       <c r="N30" s="1">
@@ -3082,11 +3085,11 @@
         <v>1000</v>
       </c>
       <c r="K31" s="27">
-        <f t="shared" ref="K31:K39" si="35">H31/31.103</f>
+        <f t="shared" ref="K31:K40" si="35">H31/31.103</f>
         <v>594.79792946018063</v>
       </c>
       <c r="L31" s="27">
-        <f t="shared" ref="L31:L39" si="36">I31/31.103</f>
+        <f t="shared" ref="L31:L40" si="36">I31/31.103</f>
         <v>562.64669002990058</v>
       </c>
       <c r="M31" s="15">
@@ -3122,7 +3125,7 @@
         <v>74499.350000000006</v>
       </c>
       <c r="F32" s="17">
-        <f t="shared" ref="F32:F39" si="37">(I32*4.03)-D32</f>
+        <f t="shared" ref="F32:F40" si="37">(I32*4.03)-D32</f>
         <v>8358.8387521000041</v>
       </c>
       <c r="G32" s="19"/>
@@ -3555,24 +3558,61 @@
       <c r="R39" s="1"/>
     </row>
     <row r="40" spans="1:19" ht="15" x14ac:dyDescent="0.2">
-      <c r="A40" s="59"/>
-      <c r="B40" s="60"/>
-      <c r="C40" s="61"/>
-      <c r="D40" s="62"/>
-      <c r="E40" s="63"/>
-      <c r="F40" s="64"/>
-      <c r="G40" s="64"/>
-      <c r="H40" s="65"/>
-      <c r="I40" s="66"/>
-      <c r="J40" s="64"/>
-      <c r="K40" s="67"/>
-      <c r="L40" s="67"/>
-      <c r="M40" s="68"/>
-      <c r="N40" s="69"/>
-      <c r="O40" s="70"/>
-      <c r="P40" s="71"/>
-      <c r="Q40" s="69"/>
-      <c r="R40" s="69"/>
+      <c r="A40" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B40" s="52"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="5">
+        <f t="shared" si="24"/>
+        <v>64683.9</v>
+      </c>
+      <c r="E40" s="22">
+        <v>75397.320000000007</v>
+      </c>
+      <c r="F40" s="17">
+        <f t="shared" si="37"/>
+        <v>2063.4673450999908</v>
+      </c>
+      <c r="G40" s="19">
+        <f>I40*4</f>
+        <v>66250.488679999995</v>
+      </c>
+      <c r="H40" s="29">
+        <v>18037.735700000001</v>
+      </c>
+      <c r="I40" s="28">
+        <v>16562.622169999999</v>
+      </c>
+      <c r="J40" s="19">
+        <f t="shared" si="31"/>
+        <v>1475.1135300000024</v>
+      </c>
+      <c r="K40" s="27">
+        <f t="shared" si="35"/>
+        <v>579.9355592708099</v>
+      </c>
+      <c r="L40" s="27">
+        <f t="shared" si="36"/>
+        <v>532.50883098093425</v>
+      </c>
+      <c r="M40" s="15">
+        <f t="shared" si="34"/>
+        <v>47.426728289875655</v>
+      </c>
+      <c r="N40" s="1">
+        <v>541.5</v>
+      </c>
+      <c r="O40" s="47"/>
+      <c r="P40" s="26">
+        <f t="shared" si="29"/>
+        <v>-38.435559270809904</v>
+      </c>
+      <c r="Q40" s="1">
+        <f t="shared" si="30"/>
+        <v>8.9911690190657509</v>
+      </c>
+      <c r="R40" s="1"/>
     </row>
     <row r="41" spans="1:19" ht="15" x14ac:dyDescent="0.2">
       <c r="A41" s="59"/>
@@ -3584,8 +3624,8 @@
       <c r="G41" s="64"/>
       <c r="H41" s="65"/>
       <c r="I41" s="66">
-        <f>I38*4.03</f>
-        <v>78321.643771800009</v>
+        <f>I40*4.03</f>
+        <v>66747.367345099992</v>
       </c>
       <c r="J41" s="64"/>
       <c r="K41" s="67"/>

--- a/gold.xlsx
+++ b/gold.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emiratessteeluae-my.sharepoint.com/personal/shakeel_awan_emsteel_com/Documents/1. Shakeel/Personel/BANK/GOLD XAU account/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="858" documentId="13_ncr:1_{851D1004-1C5D-48B9-BE48-07C0F232C6FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89465B88-AA25-48FE-81F6-C28DA2140968}"/>
+  <xr:revisionPtr revIDLastSave="1163" documentId="13_ncr:1_{851D1004-1C5D-48B9-BE48-07C0F232C6FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BA53A14-2B4B-41D9-9D3F-CD78E94C9C59}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="97">
   <si>
     <t>XAU account</t>
   </si>
@@ -253,6 +253,84 @@
   </si>
   <si>
     <t>21.03.2026</t>
+  </si>
+  <si>
+    <t>23.03.2026</t>
+  </si>
+  <si>
+    <t>26.03.2026</t>
+  </si>
+  <si>
+    <t>01.04.2026</t>
+  </si>
+  <si>
+    <t>28.03.2026</t>
+  </si>
+  <si>
+    <t>wt</t>
+  </si>
+  <si>
+    <t>amount</t>
+  </si>
+  <si>
+    <t>gold rate</t>
+  </si>
+  <si>
+    <t>avg rate with making charges</t>
+  </si>
+  <si>
+    <t>Making charges</t>
+  </si>
+  <si>
+    <t>with VAT</t>
+  </si>
+  <si>
+    <t>amount with MC</t>
+  </si>
+  <si>
+    <t>MC</t>
+  </si>
+  <si>
+    <t>total amount</t>
+  </si>
+  <si>
+    <t>biscuit</t>
+  </si>
+  <si>
+    <t>22 carat</t>
+  </si>
+  <si>
+    <t>rate 22 carat</t>
+  </si>
+  <si>
+    <t>09.03.2020</t>
+  </si>
+  <si>
+    <t>danish</t>
+  </si>
+  <si>
+    <t>with tax and vat</t>
+  </si>
+  <si>
+    <t>pkr</t>
+  </si>
+  <si>
+    <t>8.04.2026</t>
+  </si>
+  <si>
+    <t>check in morning</t>
+  </si>
+  <si>
+    <t>these rates are on 08.04.2026 after bank closing on web site and are differnet from mobile app rates</t>
+  </si>
+  <si>
+    <t>09.04.2026</t>
+  </si>
+  <si>
+    <t>15.04.2026</t>
+  </si>
+  <si>
+    <t>21.04.2026</t>
   </si>
 </sst>
 </file>
@@ -362,7 +440,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -465,11 +543,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -650,41 +767,68 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -694,6 +838,42 @@
     </xf>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1247,7 +1427,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDAADDF0-12CA-41AA-907F-C3C1F5BA90E3}">
-  <dimension ref="A1:AD46"/>
+  <dimension ref="A1:AD74"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -2719,7 +2899,7 @@
         <f>I25*4</f>
         <v>78837.207999999999</v>
       </c>
-      <c r="F25" s="17">
+      <c r="F25" s="80">
         <f t="shared" si="13"/>
         <v>14744.587059999998</v>
       </c>
@@ -2949,7 +3129,7 @@
       <c r="B29" s="52"/>
       <c r="C29" s="24"/>
       <c r="D29" s="5">
-        <f t="shared" ref="D29:D40" si="24">D28+C29</f>
+        <f t="shared" ref="D29:D43" si="24">D28+C29</f>
         <v>64683.9</v>
       </c>
       <c r="E29" s="22">
@@ -2990,11 +3170,11 @@
       </c>
       <c r="O29" s="47"/>
       <c r="P29" s="26">
-        <f t="shared" ref="P29:P40" si="29">N29-K29</f>
+        <f t="shared" ref="P29:P47" si="29">N29-K29</f>
         <v>-3.6659486223129534E-2</v>
       </c>
       <c r="Q29" s="1">
-        <f t="shared" ref="Q29:Q40" si="30">N29-L29</f>
+        <f t="shared" ref="Q29:Q47" si="30">N29-L29</f>
         <v>23.64186766549858</v>
       </c>
       <c r="R29" s="1"/>
@@ -3026,7 +3206,7 @@
         <v>16931.170989999999</v>
       </c>
       <c r="J30" s="19">
-        <f t="shared" ref="J30:J40" si="31">H30-I30</f>
+        <f t="shared" ref="J30:J47" si="31">H30-I30</f>
         <v>736.4732299999996</v>
       </c>
       <c r="K30" s="27">
@@ -3038,7 +3218,7 @@
         <v>544.35813233450142</v>
       </c>
       <c r="M30" s="15">
-        <f t="shared" ref="M30:M40" si="34">K30-L30</f>
+        <f t="shared" ref="M30:M47" si="34">K30-L30</f>
         <v>23.67852715172171</v>
       </c>
       <c r="N30" s="1">
@@ -3085,11 +3265,11 @@
         <v>1000</v>
       </c>
       <c r="K31" s="27">
-        <f t="shared" ref="K31:K40" si="35">H31/31.103</f>
+        <f t="shared" ref="K31:K47" si="35">H31/31.103</f>
         <v>594.79792946018063</v>
       </c>
       <c r="L31" s="27">
-        <f t="shared" ref="L31:L40" si="36">I31/31.103</f>
+        <f t="shared" ref="L31:L47" si="36">I31/31.103</f>
         <v>562.64669002990058</v>
       </c>
       <c r="M31" s="15">
@@ -3125,7 +3305,7 @@
         <v>74499.350000000006</v>
       </c>
       <c r="F32" s="17">
-        <f t="shared" ref="F32:F40" si="37">(I32*4.03)-D32</f>
+        <f t="shared" ref="F32:F47" si="37">(I32*4.03)-D32</f>
         <v>8358.8387521000041</v>
       </c>
       <c r="G32" s="19"/>
@@ -3518,7 +3698,7 @@
         <v>9042.4038863000096</v>
       </c>
       <c r="G39" s="19">
-        <f>I39*4</f>
+        <f t="shared" ref="G39:G59" si="38">I39*4</f>
         <v>73177.472840000002</v>
       </c>
       <c r="H39" s="29">
@@ -3575,7 +3755,7 @@
         <v>2063.4673450999908</v>
       </c>
       <c r="G40" s="19">
-        <f>I40*4</f>
+        <f t="shared" si="38"/>
         <v>66250.488679999995</v>
       </c>
       <c r="H40" s="29">
@@ -3615,111 +3795,969 @@
       <c r="R40" s="1"/>
     </row>
     <row r="41" spans="1:19" ht="15" x14ac:dyDescent="0.2">
-      <c r="A41" s="59"/>
-      <c r="B41" s="60"/>
-      <c r="C41" s="61"/>
-      <c r="D41" s="62"/>
-      <c r="E41" s="63"/>
-      <c r="F41" s="64"/>
-      <c r="G41" s="64"/>
-      <c r="H41" s="65"/>
-      <c r="I41" s="66">
-        <f>I40*4.03</f>
-        <v>66747.367345099992</v>
-      </c>
-      <c r="J41" s="64"/>
-      <c r="K41" s="67"/>
-      <c r="L41" s="67"/>
-      <c r="M41" s="68"/>
-      <c r="N41" s="69"/>
-      <c r="O41" s="70"/>
-      <c r="P41" s="71"/>
-      <c r="Q41" s="69"/>
-      <c r="R41" s="69"/>
+      <c r="A41" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B41" s="52"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="5">
+        <f t="shared" si="24"/>
+        <v>64683.9</v>
+      </c>
+      <c r="E41" s="22">
+        <v>65841.62</v>
+      </c>
+      <c r="F41" s="17">
+        <f>(I41*4.03)-D41</f>
+        <v>-4780.9172889999973</v>
+      </c>
+      <c r="G41" s="19">
+        <f t="shared" si="38"/>
+        <v>59457.054799999998</v>
+      </c>
+      <c r="H41" s="62">
+        <v>17811.478899999998</v>
+      </c>
+      <c r="I41" s="63">
+        <v>14864.2637</v>
+      </c>
+      <c r="J41" s="64">
+        <f t="shared" si="31"/>
+        <v>2947.2151999999987</v>
+      </c>
+      <c r="K41" s="65">
+        <f t="shared" si="35"/>
+        <v>572.66112272128078</v>
+      </c>
+      <c r="L41" s="65">
+        <f t="shared" si="36"/>
+        <v>477.9045011735202</v>
+      </c>
+      <c r="M41" s="66">
+        <f t="shared" si="34"/>
+        <v>94.756621547760574</v>
+      </c>
+      <c r="N41" s="67">
+        <v>530</v>
+      </c>
+      <c r="O41" s="68"/>
+      <c r="P41" s="69">
+        <f t="shared" si="29"/>
+        <v>-42.661122721280776</v>
+      </c>
+      <c r="Q41" s="67">
+        <f t="shared" si="30"/>
+        <v>52.095498826479798</v>
+      </c>
+      <c r="R41" s="60"/>
     </row>
     <row r="42" spans="1:19" ht="15" x14ac:dyDescent="0.2">
-      <c r="A42" s="59"/>
-      <c r="B42" s="60"/>
-      <c r="C42" s="61"/>
-      <c r="D42" s="62"/>
-      <c r="E42" s="63"/>
-      <c r="F42" s="64"/>
-      <c r="G42" s="64"/>
-      <c r="H42" s="65"/>
-      <c r="I42" s="66"/>
-      <c r="J42" s="64"/>
-      <c r="K42" s="67"/>
-      <c r="L42" s="67"/>
-      <c r="M42" s="68"/>
-      <c r="N42" s="69"/>
-      <c r="O42" s="70"/>
-      <c r="P42" s="71"/>
-      <c r="Q42" s="69"/>
-      <c r="R42" s="69"/>
-    </row>
-    <row r="43" spans="1:19" ht="23.25" x14ac:dyDescent="0.2">
-      <c r="C43" s="54"/>
-    </row>
-    <row r="44" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="54" t="s">
+      <c r="A42" s="59" t="s">
+        <v>72</v>
+      </c>
+      <c r="B42" s="52"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="5">
+        <f t="shared" si="24"/>
+        <v>64683.9</v>
+      </c>
+      <c r="E42" s="22">
+        <v>65841.62</v>
+      </c>
+      <c r="F42" s="17">
+        <f>(I42*4.03)-D42</f>
+        <v>-468.00318869999319</v>
+      </c>
+      <c r="G42" s="61">
+        <f t="shared" si="38"/>
+        <v>63737.862840000002</v>
+      </c>
+      <c r="H42" s="70">
+        <v>16562.805820000001</v>
+      </c>
+      <c r="I42" s="71">
+        <v>15934.46571</v>
+      </c>
+      <c r="J42" s="72">
+        <f t="shared" si="31"/>
+        <v>628.340110000001</v>
+      </c>
+      <c r="K42" s="73">
+        <f t="shared" si="35"/>
+        <v>532.51473555605571</v>
+      </c>
+      <c r="L42" s="73">
+        <f t="shared" si="36"/>
+        <v>512.31282223579717</v>
+      </c>
+      <c r="M42" s="74">
+        <f t="shared" si="34"/>
+        <v>20.201913320258541</v>
+      </c>
+      <c r="N42" s="75">
+        <v>536</v>
+      </c>
+      <c r="O42" s="76"/>
+      <c r="P42" s="77">
+        <f t="shared" si="29"/>
+        <v>3.4852644439442884</v>
+      </c>
+      <c r="Q42" s="75">
+        <f t="shared" si="30"/>
+        <v>23.687177764202829</v>
+      </c>
+      <c r="R42" s="75"/>
+    </row>
+    <row r="43" spans="1:19" ht="15" x14ac:dyDescent="0.2">
+      <c r="A43" s="59" t="s">
+        <v>73</v>
+      </c>
+      <c r="B43" s="52"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="5">
+        <f t="shared" si="24"/>
+        <v>64683.9</v>
+      </c>
+      <c r="E43" s="22">
+        <v>69350.899999999994</v>
+      </c>
+      <c r="F43" s="17">
+        <f t="shared" si="37"/>
+        <v>3396.1928832829944</v>
+      </c>
+      <c r="G43" s="61">
+        <f t="shared" si="38"/>
+        <v>67573.293184399998</v>
+      </c>
+      <c r="H43" s="70">
+        <v>17523.994291899999</v>
+      </c>
+      <c r="I43" s="71">
+        <v>16893.323296099999</v>
+      </c>
+      <c r="J43" s="72">
+        <f t="shared" si="31"/>
+        <v>630.67099579999922</v>
+      </c>
+      <c r="K43" s="73">
+        <f t="shared" si="35"/>
+        <v>563.41813625373754</v>
+      </c>
+      <c r="L43" s="73">
+        <f t="shared" si="36"/>
+        <v>543.14128206603857</v>
+      </c>
+      <c r="M43" s="74">
+        <f t="shared" si="34"/>
+        <v>20.276854187698973</v>
+      </c>
+      <c r="N43" s="75">
+        <v>567</v>
+      </c>
+      <c r="O43" s="76"/>
+      <c r="P43" s="77">
+        <f t="shared" si="29"/>
+        <v>3.5818637462624565</v>
+      </c>
+      <c r="Q43" s="75">
+        <f t="shared" si="30"/>
+        <v>23.858717933961429</v>
+      </c>
+      <c r="R43" s="75"/>
+    </row>
+    <row r="44" spans="1:19" ht="15" x14ac:dyDescent="0.2">
+      <c r="A44" s="59" t="s">
+        <v>91</v>
+      </c>
+      <c r="B44" s="52"/>
+      <c r="C44" s="24"/>
+      <c r="D44" s="5">
+        <f t="shared" ref="D44:D47" si="39">D43+C44</f>
+        <v>64683.9</v>
+      </c>
+      <c r="E44" s="22">
+        <v>71076.05</v>
+      </c>
+      <c r="F44" s="17">
+        <f t="shared" si="37"/>
+        <v>642.40000000000146</v>
+      </c>
+      <c r="G44" s="61">
+        <f t="shared" si="38"/>
+        <v>64840</v>
+      </c>
+      <c r="H44" s="70">
+        <v>18610</v>
+      </c>
+      <c r="I44" s="71">
+        <v>16210</v>
+      </c>
+      <c r="J44" s="72">
+        <f t="shared" si="31"/>
+        <v>2400</v>
+      </c>
+      <c r="K44" s="73">
+        <f t="shared" si="35"/>
+        <v>598.33456579751146</v>
+      </c>
+      <c r="L44" s="73">
+        <f t="shared" si="36"/>
+        <v>521.17159116483936</v>
+      </c>
+      <c r="M44" s="74">
+        <f t="shared" si="34"/>
+        <v>77.162974632672103</v>
+      </c>
+      <c r="N44" s="75">
+        <v>582.5</v>
+      </c>
+      <c r="O44" s="76"/>
+      <c r="P44" s="77">
+        <f t="shared" si="29"/>
+        <v>-15.834565797511459</v>
+      </c>
+      <c r="Q44" s="75">
+        <f t="shared" si="30"/>
+        <v>61.328408835160644</v>
+      </c>
+      <c r="R44" s="75"/>
+    </row>
+    <row r="45" spans="1:19" ht="15" x14ac:dyDescent="0.2">
+      <c r="A45" s="59" t="s">
+        <v>94</v>
+      </c>
+      <c r="B45" s="52"/>
+      <c r="C45" s="24"/>
+      <c r="D45" s="5">
+        <f t="shared" si="39"/>
+        <v>64683.9</v>
+      </c>
+      <c r="E45" s="22">
+        <v>69727.490000000005</v>
+      </c>
+      <c r="F45" s="17">
+        <f t="shared" si="37"/>
+        <v>3778.7451223000025</v>
+      </c>
+      <c r="G45" s="61">
+        <f t="shared" si="38"/>
+        <v>67952.997640000001</v>
+      </c>
+      <c r="H45" s="70">
+        <v>17615.965110000001</v>
+      </c>
+      <c r="I45" s="71">
+        <v>16988.24941</v>
+      </c>
+      <c r="J45" s="72">
+        <f t="shared" si="31"/>
+        <v>627.71570000000065</v>
+      </c>
+      <c r="K45" s="73">
+        <f t="shared" si="35"/>
+        <v>566.37511204706936</v>
+      </c>
+      <c r="L45" s="73">
+        <f t="shared" si="36"/>
+        <v>546.19327428222357</v>
+      </c>
+      <c r="M45" s="74">
+        <f t="shared" si="34"/>
+        <v>20.181837764845795</v>
+      </c>
+      <c r="N45" s="75">
+        <v>569</v>
+      </c>
+      <c r="O45" s="76"/>
+      <c r="P45" s="77">
+        <f t="shared" si="29"/>
+        <v>2.624887952930635</v>
+      </c>
+      <c r="Q45" s="75">
+        <f t="shared" si="30"/>
+        <v>22.80672571777643</v>
+      </c>
+      <c r="R45" s="75"/>
+    </row>
+    <row r="46" spans="1:19" ht="15" x14ac:dyDescent="0.2">
+      <c r="A46" s="59" t="s">
+        <v>95</v>
+      </c>
+      <c r="B46" s="52"/>
+      <c r="C46" s="24"/>
+      <c r="D46" s="5">
+        <f t="shared" si="39"/>
+        <v>64683.9</v>
+      </c>
+      <c r="E46" s="22">
+        <v>71215.56</v>
+      </c>
+      <c r="F46" s="17">
+        <f t="shared" si="37"/>
+        <v>4006.4028045000086</v>
+      </c>
+      <c r="G46" s="61">
+        <f t="shared" si="38"/>
+        <v>68178.960600000006</v>
+      </c>
+      <c r="H46" s="70">
+        <v>18297.96775</v>
+      </c>
+      <c r="I46" s="71">
+        <v>17044.740150000001</v>
+      </c>
+      <c r="J46" s="72">
+        <f t="shared" si="31"/>
+        <v>1253.2275999999983</v>
+      </c>
+      <c r="K46" s="73">
+        <f t="shared" si="35"/>
+        <v>588.30234221779244</v>
+      </c>
+      <c r="L46" s="73">
+        <f t="shared" si="36"/>
+        <v>548.00952158955727</v>
+      </c>
+      <c r="M46" s="74">
+        <f t="shared" si="34"/>
+        <v>40.292820628235177</v>
+      </c>
+      <c r="N46" s="75">
+        <v>578</v>
+      </c>
+      <c r="O46" s="76"/>
+      <c r="P46" s="77">
+        <f t="shared" si="29"/>
+        <v>-10.302342217792443</v>
+      </c>
+      <c r="Q46" s="75">
+        <f t="shared" si="30"/>
+        <v>29.990478410442734</v>
+      </c>
+      <c r="R46" s="75"/>
+    </row>
+    <row r="47" spans="1:19" ht="15" x14ac:dyDescent="0.2">
+      <c r="A47" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="B47" s="52"/>
+      <c r="C47" s="24"/>
+      <c r="D47" s="5">
+        <f t="shared" si="39"/>
+        <v>64683.9</v>
+      </c>
+      <c r="E47" s="22">
+        <v>70733.23</v>
+      </c>
+      <c r="F47" s="17">
+        <f t="shared" si="37"/>
+        <v>3524.591520000009</v>
+      </c>
+      <c r="G47" s="61">
+        <f t="shared" si="38"/>
+        <v>67700.736000000004</v>
+      </c>
+      <c r="H47" s="70">
+        <v>18178.154490000001</v>
+      </c>
+      <c r="I47" s="71">
+        <v>16925.184000000001</v>
+      </c>
+      <c r="J47" s="72">
+        <f t="shared" si="31"/>
+        <v>1252.9704899999997</v>
+      </c>
+      <c r="K47" s="73">
+        <f t="shared" si="35"/>
+        <v>584.45019740861005</v>
+      </c>
+      <c r="L47" s="73">
+        <f t="shared" si="36"/>
+        <v>544.16564318554481</v>
+      </c>
+      <c r="M47" s="74">
+        <f t="shared" si="34"/>
+        <v>40.284554223065243</v>
+      </c>
+      <c r="N47" s="75">
+        <v>572.25</v>
+      </c>
+      <c r="O47" s="76"/>
+      <c r="P47" s="77">
+        <f t="shared" si="29"/>
+        <v>-12.200197408610052</v>
+      </c>
+      <c r="Q47" s="75">
+        <f t="shared" si="30"/>
+        <v>28.084356814455191</v>
+      </c>
+      <c r="R47" s="75"/>
+    </row>
+    <row r="48" spans="1:19" ht="15" x14ac:dyDescent="0.2">
+      <c r="A48" s="59"/>
+      <c r="B48" s="84"/>
+      <c r="C48" s="85"/>
+      <c r="D48" s="86"/>
+      <c r="E48" s="87"/>
+      <c r="F48" s="88"/>
+      <c r="G48" s="88"/>
+      <c r="H48" s="89"/>
+      <c r="I48" s="90"/>
+      <c r="J48" s="88"/>
+      <c r="K48" s="91"/>
+      <c r="L48" s="91"/>
+      <c r="M48" s="92"/>
+      <c r="N48" s="93"/>
+      <c r="O48" s="94"/>
+      <c r="P48" s="95"/>
+      <c r="Q48" s="93"/>
+      <c r="R48" s="93"/>
+    </row>
+    <row r="49" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+      <c r="A49" s="59"/>
+      <c r="B49" s="84"/>
+      <c r="C49" s="85"/>
+      <c r="D49" s="86"/>
+      <c r="E49" s="87"/>
+      <c r="F49" s="88"/>
+      <c r="G49" s="88"/>
+      <c r="H49" s="89"/>
+      <c r="I49" s="90"/>
+      <c r="J49" s="88"/>
+      <c r="K49" s="91"/>
+      <c r="L49" s="91"/>
+      <c r="M49" s="92"/>
+      <c r="N49" s="93"/>
+      <c r="O49" s="94"/>
+      <c r="P49" s="95"/>
+      <c r="Q49" s="93"/>
+      <c r="R49" s="93"/>
+    </row>
+    <row r="50" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+      <c r="A50" s="59"/>
+      <c r="B50" s="84"/>
+      <c r="C50" s="85"/>
+      <c r="D50" s="86"/>
+      <c r="E50" s="87"/>
+      <c r="F50" s="88"/>
+      <c r="G50" s="88"/>
+      <c r="H50" s="89"/>
+      <c r="I50" s="90"/>
+      <c r="J50" s="88"/>
+      <c r="K50" s="91"/>
+      <c r="L50" s="91"/>
+      <c r="M50" s="92"/>
+      <c r="N50" s="93"/>
+      <c r="O50" s="94"/>
+      <c r="P50" s="95"/>
+      <c r="Q50" s="93"/>
+      <c r="R50" s="93"/>
+    </row>
+    <row r="51" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+      <c r="A51" s="59"/>
+      <c r="B51" s="84"/>
+      <c r="C51" s="85"/>
+      <c r="D51" s="86"/>
+      <c r="E51" s="87"/>
+      <c r="F51" s="88"/>
+      <c r="G51" s="88"/>
+      <c r="H51" s="89"/>
+      <c r="I51" s="90"/>
+      <c r="J51" s="88"/>
+      <c r="K51" s="91"/>
+      <c r="L51" s="91"/>
+      <c r="M51" s="92"/>
+      <c r="N51" s="93"/>
+      <c r="O51" s="94"/>
+      <c r="P51" s="95"/>
+      <c r="Q51" s="93"/>
+      <c r="R51" s="93"/>
+    </row>
+    <row r="52" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+      <c r="A52" s="59"/>
+      <c r="B52" s="84"/>
+      <c r="C52" s="85"/>
+      <c r="D52" s="86"/>
+      <c r="E52" s="87"/>
+      <c r="F52" s="88"/>
+      <c r="G52" s="88"/>
+      <c r="H52" s="89"/>
+      <c r="I52" s="90"/>
+      <c r="J52" s="88"/>
+      <c r="K52" s="91"/>
+      <c r="L52" s="91"/>
+      <c r="M52" s="92"/>
+      <c r="N52" s="93"/>
+      <c r="O52" s="94"/>
+      <c r="P52" s="95"/>
+      <c r="Q52" s="93"/>
+      <c r="R52" s="93"/>
+    </row>
+    <row r="53" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+      <c r="A53" s="59"/>
+      <c r="B53" s="84"/>
+      <c r="C53" s="85"/>
+      <c r="D53" s="86"/>
+      <c r="E53" s="87"/>
+      <c r="F53" s="88"/>
+      <c r="G53" s="88"/>
+      <c r="H53" s="89"/>
+      <c r="I53" s="90"/>
+      <c r="J53" s="88"/>
+      <c r="K53" s="91"/>
+      <c r="L53" s="91"/>
+      <c r="M53" s="92"/>
+      <c r="N53" s="93"/>
+      <c r="O53" s="94"/>
+      <c r="P53" s="95"/>
+      <c r="Q53" s="93"/>
+      <c r="R53" s="93"/>
+    </row>
+    <row r="54" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+      <c r="A54" s="59"/>
+      <c r="B54" s="84"/>
+      <c r="C54" s="85"/>
+      <c r="D54" s="86"/>
+      <c r="E54" s="87"/>
+      <c r="F54" s="88"/>
+      <c r="G54" s="88"/>
+      <c r="H54" s="89"/>
+      <c r="I54" s="90"/>
+      <c r="J54" s="88"/>
+      <c r="K54" s="91"/>
+      <c r="L54" s="91"/>
+      <c r="M54" s="92"/>
+      <c r="N54" s="93"/>
+      <c r="O54" s="94"/>
+      <c r="P54" s="95"/>
+      <c r="Q54" s="93"/>
+      <c r="R54" s="93"/>
+    </row>
+    <row r="55" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+      <c r="A55" s="59"/>
+      <c r="B55" s="84"/>
+      <c r="C55" s="85"/>
+      <c r="D55" s="86"/>
+      <c r="E55" s="87"/>
+      <c r="F55" s="88"/>
+      <c r="G55" s="88"/>
+      <c r="H55" s="89"/>
+      <c r="I55" s="90"/>
+      <c r="J55" s="88"/>
+      <c r="K55" s="91"/>
+      <c r="L55" s="91"/>
+      <c r="M55" s="92"/>
+      <c r="N55" s="93"/>
+      <c r="O55" s="94"/>
+      <c r="P55" s="95"/>
+      <c r="Q55" s="93"/>
+      <c r="R55" s="93"/>
+    </row>
+    <row r="56" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+      <c r="A56" s="59"/>
+      <c r="B56" s="84"/>
+      <c r="C56" s="85"/>
+      <c r="D56" s="86"/>
+      <c r="E56" s="87"/>
+      <c r="F56" s="88"/>
+      <c r="G56" s="88"/>
+      <c r="H56" s="89"/>
+      <c r="I56" s="90"/>
+      <c r="J56" s="88"/>
+      <c r="K56" s="91"/>
+      <c r="L56" s="91"/>
+      <c r="M56" s="92"/>
+      <c r="N56" s="93"/>
+      <c r="O56" s="94"/>
+      <c r="P56" s="95"/>
+      <c r="Q56" s="93"/>
+      <c r="R56" s="93"/>
+    </row>
+    <row r="57" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+      <c r="A57" s="59"/>
+      <c r="B57" s="84"/>
+      <c r="C57" s="85"/>
+      <c r="D57" s="86"/>
+      <c r="E57" s="87"/>
+      <c r="F57" s="88"/>
+      <c r="G57" s="88"/>
+      <c r="H57" s="89"/>
+      <c r="I57" s="90"/>
+      <c r="J57" s="88"/>
+      <c r="K57" s="91"/>
+      <c r="L57" s="91"/>
+      <c r="M57" s="92"/>
+      <c r="N57" s="93"/>
+      <c r="O57" s="94"/>
+      <c r="P57" s="95"/>
+      <c r="Q57" s="93"/>
+      <c r="R57" s="93"/>
+    </row>
+    <row r="58" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+      <c r="A58" s="59"/>
+      <c r="B58" s="84"/>
+      <c r="C58" s="85"/>
+      <c r="D58" s="86"/>
+      <c r="E58" s="87"/>
+      <c r="F58" s="88"/>
+      <c r="G58" s="88"/>
+      <c r="H58" s="89"/>
+      <c r="I58" s="90"/>
+      <c r="J58" s="88"/>
+      <c r="K58" s="91"/>
+      <c r="L58" s="91"/>
+      <c r="M58" s="92"/>
+      <c r="N58" s="93"/>
+      <c r="O58" s="94"/>
+      <c r="P58" s="95"/>
+      <c r="Q58" s="93"/>
+      <c r="R58" s="93"/>
+    </row>
+    <row r="59" spans="1:18" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="C44" s="54" t="s">
+      <c r="C59" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="D44" s="53"/>
-      <c r="E44" s="53"/>
-      <c r="F44" s="53">
-        <f>H44*4</f>
+      <c r="D59" s="53"/>
+      <c r="E59" s="53"/>
+      <c r="F59" s="53">
+        <f>H59*4</f>
         <v>72521.475040000005</v>
       </c>
-      <c r="G44" s="53">
-        <f>I44*4</f>
+      <c r="G59" s="53">
+        <f t="shared" si="38"/>
         <v>77112.871960000004</v>
       </c>
-      <c r="H44" s="58">
+      <c r="H59" s="58">
         <v>18130.368760000001</v>
       </c>
-      <c r="I44">
+      <c r="I59">
         <v>19278.217990000001</v>
       </c>
-      <c r="J44">
+      <c r="J59">
         <v>727521.48</v>
       </c>
     </row>
-    <row r="45" spans="1:19" ht="23.25" x14ac:dyDescent="0.2">
-      <c r="A45" s="53"/>
-      <c r="B45" s="54" t="s">
+    <row r="60" spans="1:18" ht="23.25" x14ac:dyDescent="0.2">
+      <c r="A60" s="53"/>
+      <c r="B60" s="54" t="s">
         <v>51</v>
       </c>
-      <c r="C45" s="54">
+      <c r="C60" s="54">
         <f>I22*4</f>
         <v>72697.809880000001</v>
       </c>
-      <c r="D45" s="54" t="s">
+      <c r="D60" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="E45" s="53"/>
-      <c r="F45" s="55"/>
-      <c r="I45">
-        <f>I36*4</f>
-        <v>74604.506800000003</v>
-      </c>
-    </row>
-    <row r="46" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="54" t="s">
+      <c r="E60" s="53"/>
+      <c r="F60" s="55"/>
+      <c r="H60" s="58">
+        <v>18005.009269999999</v>
+      </c>
+      <c r="I60" s="58">
+        <v>17374.722470000001</v>
+      </c>
+      <c r="J60" s="45" t="s">
+        <v>92</v>
+      </c>
+      <c r="K60" s="45" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B61" s="54" t="s">
         <v>50</v>
       </c>
-      <c r="C46" s="54">
-        <f>C45-D23</f>
+      <c r="C61" s="54">
+        <f>C60-D23</f>
         <v>8013.9098799999992</v>
       </c>
-      <c r="D46" s="54" t="s">
+      <c r="D61" s="54" t="s">
         <v>52</v>
       </c>
     </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="E63" t="s">
+        <v>77</v>
+      </c>
+      <c r="F63" t="s">
+        <v>75</v>
+      </c>
+      <c r="G63" t="s">
+        <v>76</v>
+      </c>
+      <c r="H63" s="45" t="s">
+        <v>79</v>
+      </c>
+      <c r="I63" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="J63" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="K63" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="L63" s="45" t="s">
+        <v>83</v>
+      </c>
+      <c r="M63" t="s">
+        <v>78</v>
+      </c>
+      <c r="O63" s="45" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="C64" t="s">
+        <v>74</v>
+      </c>
+      <c r="E64">
+        <v>501.25</v>
+      </c>
+      <c r="F64">
+        <v>6.2</v>
+      </c>
+      <c r="G64" s="7">
+        <f>E64*F64</f>
+        <v>3107.75</v>
+      </c>
+      <c r="H64" s="79">
+        <v>7.9000000000000001E-2</v>
+      </c>
+      <c r="I64" s="78">
+        <f>G64*H64</f>
+        <v>245.51224999999999</v>
+      </c>
+      <c r="J64" s="7">
+        <f>I64+G64</f>
+        <v>3353.2622499999998</v>
+      </c>
+      <c r="K64" s="7">
+        <f>5%*(G64+I64)</f>
+        <v>167.66311250000001</v>
+      </c>
+      <c r="L64" s="78">
+        <f>(E64*F64)+I64+K64</f>
+        <v>3520.9253624999997</v>
+      </c>
+      <c r="M64" s="7">
+        <f>L64/F64</f>
+        <v>567.89118749999989</v>
+      </c>
+      <c r="O64">
+        <v>525</v>
+      </c>
+      <c r="P64" s="45" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="65" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C65" t="s">
+        <v>74</v>
+      </c>
+      <c r="E65">
+        <v>501.25</v>
+      </c>
+      <c r="F65">
+        <v>6.23</v>
+      </c>
+      <c r="G65" s="7">
+        <f>E65*F65</f>
+        <v>3122.7875000000004</v>
+      </c>
+      <c r="H65" s="79">
+        <v>7.9000000000000001E-2</v>
+      </c>
+      <c r="I65" s="78">
+        <f>E65*F65*H65</f>
+        <v>246.70021250000002</v>
+      </c>
+      <c r="J65" s="7">
+        <f t="shared" ref="J65:J67" si="40">I65+G65</f>
+        <v>3369.4877125000003</v>
+      </c>
+      <c r="K65" s="7">
+        <f>5%*(G65+I65)</f>
+        <v>168.47438562500002</v>
+      </c>
+      <c r="L65" s="78">
+        <f>(E65*F65)+I65+K65</f>
+        <v>3537.9620981250005</v>
+      </c>
+      <c r="M65" s="7">
+        <f>L65/F65</f>
+        <v>567.8911875</v>
+      </c>
+    </row>
+    <row r="66" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C66" t="s">
+        <v>74</v>
+      </c>
+      <c r="E66">
+        <v>501.25</v>
+      </c>
+      <c r="F66">
+        <v>7.75</v>
+      </c>
+      <c r="G66" s="7">
+        <f t="shared" ref="G66:G68" si="41">E66*F66</f>
+        <v>3884.6875</v>
+      </c>
+      <c r="H66" s="79">
+        <v>5.67E-2</v>
+      </c>
+      <c r="I66" s="78">
+        <f t="shared" ref="I66:I67" si="42">E66*F66*H66</f>
+        <v>220.26178125000001</v>
+      </c>
+      <c r="J66" s="7">
+        <f t="shared" si="40"/>
+        <v>4104.9492812500002</v>
+      </c>
+      <c r="K66" s="7">
+        <f>5%*(G66+I66)</f>
+        <v>205.24746406250003</v>
+      </c>
+      <c r="L66" s="78">
+        <f>(E66*F66)+I66+K66</f>
+        <v>4310.1967453124998</v>
+      </c>
+      <c r="M66" s="7">
+        <f>L66/F66</f>
+        <v>556.15441874999999</v>
+      </c>
+    </row>
+    <row r="67" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C67" t="s">
+        <v>74</v>
+      </c>
+      <c r="E67">
+        <v>501.25</v>
+      </c>
+      <c r="F67">
+        <v>7.57</v>
+      </c>
+      <c r="G67" s="7">
+        <f t="shared" si="41"/>
+        <v>3794.4625000000001</v>
+      </c>
+      <c r="H67" s="79">
+        <v>5.67E-2</v>
+      </c>
+      <c r="I67" s="78">
+        <f t="shared" si="42"/>
+        <v>215.14602375000001</v>
+      </c>
+      <c r="J67" s="7">
+        <f t="shared" si="40"/>
+        <v>4009.6085237500001</v>
+      </c>
+      <c r="K67" s="7">
+        <f>5%*(G67+I67)</f>
+        <v>200.48042618750003</v>
+      </c>
+      <c r="L67" s="78">
+        <f>(E67*F67)+I67+K67</f>
+        <v>4210.0889499374998</v>
+      </c>
+      <c r="M67" s="7">
+        <f>L67/F67</f>
+        <v>556.15441874999999</v>
+      </c>
+    </row>
+    <row r="68" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C68" t="s">
+        <v>74</v>
+      </c>
+      <c r="E68">
+        <v>541.25</v>
+      </c>
+      <c r="F68">
+        <v>20</v>
+      </c>
+      <c r="G68">
+        <f t="shared" si="41"/>
+        <v>10825</v>
+      </c>
+      <c r="I68">
+        <v>135</v>
+      </c>
+      <c r="L68" s="78">
+        <f>(E68*F68)+I68+K68</f>
+        <v>10960</v>
+      </c>
+      <c r="M68" s="7">
+        <f>L68/F68</f>
+        <v>548</v>
+      </c>
+      <c r="N68" s="45" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="71" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="J71" s="78">
+        <f>(D71*E71)+H71+I71</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="H72" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="I72" s="45" t="s">
+        <v>86</v>
+      </c>
+      <c r="K72" s="45" t="s">
+        <v>89</v>
+      </c>
+      <c r="L72" s="45" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="73" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="F73" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="G73" s="45" t="s">
+        <v>87</v>
+      </c>
+      <c r="H73">
+        <v>139.63</v>
+      </c>
+      <c r="I73">
+        <v>190.25</v>
+      </c>
+      <c r="J73">
+        <f>H73*I73</f>
+        <v>26564.607499999998</v>
+      </c>
+      <c r="K73">
+        <v>32000</v>
+      </c>
+      <c r="L73">
+        <f>K73*76</f>
+        <v>2432000</v>
+      </c>
+    </row>
+    <row r="74" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="I74">
+        <v>525</v>
+      </c>
+      <c r="J74">
+        <f>I74*H73</f>
+        <v>73305.75</v>
+      </c>
+      <c r="L74">
+        <f>J74*76</f>
+        <v>5571237</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="F3:F42">
+  <conditionalFormatting sqref="F3:F58">
     <cfRule type="cellIs" dxfId="19" priority="6" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -3753,7 +4791,7 @@
       <formula>"D11&lt;D12"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G28:G42">
+  <conditionalFormatting sqref="G28:G58">
     <cfRule type="cellIs" dxfId="9" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -3956,10 +4994,10 @@
       <c r="G7" s="40"/>
       <c r="H7" s="40"/>
       <c r="I7" s="40"/>
-      <c r="J7" s="74" t="s">
+      <c r="J7" s="83" t="s">
         <v>3</v>
       </c>
-      <c r="K7" s="74"/>
+      <c r="K7" s="83"/>
       <c r="L7" s="40"/>
       <c r="M7" s="40"/>
       <c r="N7" s="40"/>
@@ -5289,8 +6327,8 @@
       <c r="A32" s="3"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
-      <c r="D32" s="72"/>
-      <c r="E32" s="73"/>
+      <c r="D32" s="81"/>
+      <c r="E32" s="82"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
@@ -5311,8 +6349,8 @@
       <c r="A33" s="3"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="72"/>
-      <c r="E33" s="73"/>
+      <c r="D33" s="81"/>
+      <c r="E33" s="82"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
@@ -5333,8 +6371,8 @@
       <c r="A34" s="3"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
-      <c r="D34" s="72"/>
-      <c r="E34" s="73"/>
+      <c r="D34" s="81"/>
+      <c r="E34" s="82"/>
       <c r="F34" s="46"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
@@ -5355,8 +6393,8 @@
       <c r="A35" s="3"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
-      <c r="D35" s="72"/>
-      <c r="E35" s="73"/>
+      <c r="D35" s="81"/>
+      <c r="E35" s="82"/>
       <c r="F35" s="2"/>
       <c r="G35" s="29"/>
       <c r="H35" s="29"/>

--- a/gold.xlsx
+++ b/gold.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emiratessteeluae-my.sharepoint.com/personal/shakeel_awan_emsteel_com/Documents/1. Shakeel/Personel/BANK/GOLD XAU account/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1163" documentId="13_ncr:1_{851D1004-1C5D-48B9-BE48-07C0F232C6FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BA53A14-2B4B-41D9-9D3F-CD78E94C9C59}"/>
+  <xr:revisionPtr revIDLastSave="1216" documentId="13_ncr:1_{851D1004-1C5D-48B9-BE48-07C0F232C6FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{528D0C50-68CF-4A6E-B504-77A52E405494}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="3" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="102">
   <si>
     <t>XAU account</t>
   </si>
@@ -331,6 +331,21 @@
   </si>
   <si>
     <t>21.04.2026</t>
+  </si>
+  <si>
+    <t>30.04.2026</t>
+  </si>
+  <si>
+    <t>07.06.2026</t>
+  </si>
+  <si>
+    <t>10.06.2026</t>
+  </si>
+  <si>
+    <t>25.06.2026</t>
+  </si>
+  <si>
+    <t>avg</t>
   </si>
 </sst>
 </file>
@@ -830,6 +845,42 @@
     <xf numFmtId="166" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="2" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -838,42 +889,6 @@
     </xf>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1134,10 +1149,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1526,7 +1537,7 @@
     </row>
     <row r="2" spans="1:30" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
-        <v>45908</v>
+        <v>686</v>
       </c>
       <c r="B2" s="51">
         <v>1</v>
@@ -3170,11 +3181,11 @@
       </c>
       <c r="O29" s="47"/>
       <c r="P29" s="26">
-        <f t="shared" ref="P29:P47" si="29">N29-K29</f>
+        <f t="shared" ref="P29:P48" si="29">N29-K29</f>
         <v>-3.6659486223129534E-2</v>
       </c>
       <c r="Q29" s="1">
-        <f t="shared" ref="Q29:Q47" si="30">N29-L29</f>
+        <f t="shared" ref="Q29:Q48" si="30">N29-L29</f>
         <v>23.64186766549858</v>
       </c>
       <c r="R29" s="1"/>
@@ -3206,7 +3217,7 @@
         <v>16931.170989999999</v>
       </c>
       <c r="J30" s="19">
-        <f t="shared" ref="J30:J47" si="31">H30-I30</f>
+        <f t="shared" ref="J30:J48" si="31">H30-I30</f>
         <v>736.4732299999996</v>
       </c>
       <c r="K30" s="27">
@@ -3218,7 +3229,7 @@
         <v>544.35813233450142</v>
       </c>
       <c r="M30" s="15">
-        <f t="shared" ref="M30:M47" si="34">K30-L30</f>
+        <f t="shared" ref="M30:M48" si="34">K30-L30</f>
         <v>23.67852715172171</v>
       </c>
       <c r="N30" s="1">
@@ -3265,11 +3276,11 @@
         <v>1000</v>
       </c>
       <c r="K31" s="27">
-        <f t="shared" ref="K31:K47" si="35">H31/31.103</f>
+        <f t="shared" ref="K31:K48" si="35">H31/31.103</f>
         <v>594.79792946018063</v>
       </c>
       <c r="L31" s="27">
-        <f t="shared" ref="L31:L47" si="36">I31/31.103</f>
+        <f t="shared" ref="L31:L48" si="36">I31/31.103</f>
         <v>562.64669002990058</v>
       </c>
       <c r="M31" s="15">
@@ -3305,7 +3316,7 @@
         <v>74499.350000000006</v>
       </c>
       <c r="F32" s="17">
-        <f t="shared" ref="F32:F47" si="37">(I32*4.03)-D32</f>
+        <f t="shared" ref="F32:F48" si="37">(I32*4.03)-D32</f>
         <v>8358.8387521000041</v>
       </c>
       <c r="G32" s="19"/>
@@ -3972,7 +3983,7 @@
       <c r="B44" s="52"/>
       <c r="C44" s="24"/>
       <c r="D44" s="5">
-        <f t="shared" ref="D44:D47" si="39">D43+C44</f>
+        <f t="shared" ref="D44:D48" si="39">D43+C44</f>
         <v>64683.9</v>
       </c>
       <c r="E44" s="22">
@@ -4194,224 +4205,377 @@
       <c r="R47" s="75"/>
     </row>
     <row r="48" spans="1:19" ht="15" x14ac:dyDescent="0.2">
-      <c r="A48" s="59"/>
-      <c r="B48" s="84"/>
-      <c r="C48" s="85"/>
-      <c r="D48" s="86"/>
-      <c r="E48" s="87"/>
-      <c r="F48" s="88"/>
-      <c r="G48" s="88"/>
-      <c r="H48" s="89"/>
-      <c r="I48" s="90"/>
-      <c r="J48" s="88"/>
-      <c r="K48" s="91"/>
-      <c r="L48" s="91"/>
-      <c r="M48" s="92"/>
-      <c r="N48" s="93"/>
-      <c r="O48" s="94"/>
-      <c r="P48" s="95"/>
-      <c r="Q48" s="93"/>
-      <c r="R48" s="93"/>
+      <c r="A48" s="59" t="s">
+        <v>97</v>
+      </c>
+      <c r="B48" s="52"/>
+      <c r="C48" s="24"/>
+      <c r="D48" s="5">
+        <f t="shared" si="39"/>
+        <v>64683.9</v>
+      </c>
+      <c r="E48" s="22">
+        <v>68688.600000000006</v>
+      </c>
+      <c r="F48" s="17">
+        <f t="shared" si="37"/>
+        <v>1482.9254532999985</v>
+      </c>
+      <c r="G48" s="61">
+        <f t="shared" si="38"/>
+        <v>65674.26844</v>
+      </c>
+      <c r="H48" s="70">
+        <v>17670.684000000001</v>
+      </c>
+      <c r="I48" s="71">
+        <v>16418.56711</v>
+      </c>
+      <c r="J48" s="72">
+        <f t="shared" si="31"/>
+        <v>1252.1168900000011</v>
+      </c>
+      <c r="K48" s="73">
+        <f t="shared" si="35"/>
+        <v>568.13439218081862</v>
+      </c>
+      <c r="L48" s="73">
+        <f t="shared" si="36"/>
+        <v>527.87728225573096</v>
+      </c>
+      <c r="M48" s="74">
+        <f t="shared" si="34"/>
+        <v>40.257109925087661</v>
+      </c>
+      <c r="N48" s="75">
+        <v>551</v>
+      </c>
+      <c r="O48" s="76"/>
+      <c r="P48" s="77">
+        <f t="shared" si="29"/>
+        <v>-17.134392180818622</v>
+      </c>
+      <c r="Q48" s="75">
+        <f t="shared" si="30"/>
+        <v>23.122717744269039</v>
+      </c>
+      <c r="R48" s="75"/>
     </row>
     <row r="49" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="A49" s="59"/>
-      <c r="B49" s="84"/>
-      <c r="C49" s="85"/>
-      <c r="D49" s="86"/>
-      <c r="E49" s="87"/>
-      <c r="F49" s="88"/>
-      <c r="G49" s="88"/>
-      <c r="H49" s="89"/>
-      <c r="I49" s="90"/>
-      <c r="J49" s="88"/>
-      <c r="K49" s="91"/>
-      <c r="L49" s="91"/>
-      <c r="M49" s="92"/>
-      <c r="N49" s="93"/>
-      <c r="O49" s="94"/>
-      <c r="P49" s="95"/>
-      <c r="Q49" s="93"/>
-      <c r="R49" s="93"/>
+      <c r="A49" s="59" t="s">
+        <v>98</v>
+      </c>
+      <c r="B49" s="52"/>
+      <c r="C49" s="24"/>
+      <c r="D49" s="5">
+        <f t="shared" ref="D49:D51" si="40">D48+C49</f>
+        <v>64683.9</v>
+      </c>
+      <c r="E49" s="22">
+        <v>65327.17</v>
+      </c>
+      <c r="F49" s="17">
+        <f t="shared" ref="F49:F51" si="41">(I49*4.03)-D49</f>
+        <v>-11286.400000000001</v>
+      </c>
+      <c r="G49" s="61">
+        <f t="shared" ref="G49:G51" si="42">I49*4</f>
+        <v>53000</v>
+      </c>
+      <c r="H49" s="70">
+        <v>18750</v>
+      </c>
+      <c r="I49" s="71">
+        <v>13250</v>
+      </c>
+      <c r="J49" s="72">
+        <f t="shared" ref="J49:J51" si="43">H49-I49</f>
+        <v>5500</v>
+      </c>
+      <c r="K49" s="73">
+        <f t="shared" ref="K49:K51" si="44">H49/31.103</f>
+        <v>602.83573931775072</v>
+      </c>
+      <c r="L49" s="73">
+        <f t="shared" ref="L49:L51" si="45">I49/31.103</f>
+        <v>426.00392245121049</v>
+      </c>
+      <c r="M49" s="74">
+        <f t="shared" ref="M49:M51" si="46">K49-L49</f>
+        <v>176.83181686654024</v>
+      </c>
+      <c r="N49" s="75">
+        <v>521</v>
+      </c>
+      <c r="O49" s="76"/>
+      <c r="P49" s="77">
+        <f t="shared" ref="P49:P51" si="47">N49-K49</f>
+        <v>-81.835739317750722</v>
+      </c>
+      <c r="Q49" s="75">
+        <f t="shared" ref="Q49:Q51" si="48">N49-L49</f>
+        <v>94.996077548789515</v>
+      </c>
+      <c r="R49" s="75"/>
     </row>
     <row r="50" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="A50" s="59"/>
-      <c r="B50" s="84"/>
-      <c r="C50" s="85"/>
-      <c r="D50" s="86"/>
-      <c r="E50" s="87"/>
-      <c r="F50" s="88"/>
-      <c r="G50" s="88"/>
-      <c r="H50" s="89"/>
-      <c r="I50" s="90"/>
-      <c r="J50" s="88"/>
-      <c r="K50" s="91"/>
-      <c r="L50" s="91"/>
-      <c r="M50" s="92"/>
-      <c r="N50" s="93"/>
-      <c r="O50" s="94"/>
-      <c r="P50" s="95"/>
-      <c r="Q50" s="93"/>
-      <c r="R50" s="93"/>
+      <c r="A50" s="59" t="s">
+        <v>99</v>
+      </c>
+      <c r="B50" s="52"/>
+      <c r="C50" s="24"/>
+      <c r="D50" s="5">
+        <f t="shared" si="40"/>
+        <v>64683.9</v>
+      </c>
+      <c r="E50" s="22">
+        <v>61477.71</v>
+      </c>
+      <c r="F50" s="17">
+        <f t="shared" si="41"/>
+        <v>-5726.3331642999983</v>
+      </c>
+      <c r="G50" s="61">
+        <f t="shared" si="42"/>
+        <v>58518.676760000002</v>
+      </c>
+      <c r="H50" s="70">
+        <v>15880.362419999999</v>
+      </c>
+      <c r="I50" s="71">
+        <v>14629.669190000001</v>
+      </c>
+      <c r="J50" s="72">
+        <f t="shared" si="43"/>
+        <v>1250.6932299999989</v>
+      </c>
+      <c r="K50" s="73">
+        <f t="shared" si="44"/>
+        <v>510.57333440504129</v>
+      </c>
+      <c r="L50" s="73">
+        <f t="shared" si="45"/>
+        <v>470.36199691348099</v>
+      </c>
+      <c r="M50" s="74">
+        <f t="shared" si="46"/>
+        <v>40.2113374915603</v>
+      </c>
+      <c r="N50" s="75">
+        <v>507</v>
+      </c>
+      <c r="O50" s="76"/>
+      <c r="P50" s="77">
+        <f t="shared" si="47"/>
+        <v>-3.5733344050412938</v>
+      </c>
+      <c r="Q50" s="75">
+        <f t="shared" si="48"/>
+        <v>36.638003086519007</v>
+      </c>
+      <c r="R50" s="75"/>
     </row>
     <row r="51" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="A51" s="59"/>
-      <c r="B51" s="84"/>
-      <c r="C51" s="85"/>
-      <c r="D51" s="86"/>
-      <c r="E51" s="87"/>
-      <c r="F51" s="88"/>
-      <c r="G51" s="88"/>
-      <c r="H51" s="89"/>
-      <c r="I51" s="90"/>
-      <c r="J51" s="88"/>
-      <c r="K51" s="91"/>
-      <c r="L51" s="91"/>
-      <c r="M51" s="92"/>
-      <c r="N51" s="93"/>
-      <c r="O51" s="94"/>
-      <c r="P51" s="95"/>
-      <c r="Q51" s="93"/>
-      <c r="R51" s="93"/>
+      <c r="A51" s="59" t="s">
+        <v>100</v>
+      </c>
+      <c r="B51" s="52"/>
+      <c r="C51" s="24"/>
+      <c r="D51" s="5">
+        <f t="shared" si="40"/>
+        <v>64683.9</v>
+      </c>
+      <c r="E51" s="22">
+        <v>59058.15</v>
+      </c>
+      <c r="F51" s="17">
+        <f t="shared" si="41"/>
+        <v>-13905.900000000001</v>
+      </c>
+      <c r="G51" s="61">
+        <f t="shared" si="42"/>
+        <v>50400</v>
+      </c>
+      <c r="H51" s="70">
+        <v>16600</v>
+      </c>
+      <c r="I51" s="71">
+        <v>12600</v>
+      </c>
+      <c r="J51" s="72">
+        <f t="shared" si="43"/>
+        <v>4000</v>
+      </c>
+      <c r="K51" s="73">
+        <f t="shared" si="44"/>
+        <v>533.7105745426486</v>
+      </c>
+      <c r="L51" s="73">
+        <f t="shared" si="45"/>
+        <v>405.10561682152843</v>
+      </c>
+      <c r="M51" s="74">
+        <f t="shared" si="46"/>
+        <v>128.60495772112017</v>
+      </c>
+      <c r="N51" s="75">
+        <v>480.75</v>
+      </c>
+      <c r="O51" s="76"/>
+      <c r="P51" s="77">
+        <f t="shared" si="47"/>
+        <v>-52.960574542648601</v>
+      </c>
+      <c r="Q51" s="75">
+        <f t="shared" si="48"/>
+        <v>75.644383178471571</v>
+      </c>
+      <c r="R51" s="75"/>
     </row>
     <row r="52" spans="1:18" ht="15" x14ac:dyDescent="0.2">
       <c r="A52" s="59"/>
-      <c r="B52" s="84"/>
-      <c r="C52" s="85"/>
-      <c r="D52" s="86"/>
-      <c r="E52" s="87"/>
-      <c r="F52" s="88"/>
-      <c r="G52" s="88"/>
-      <c r="H52" s="89"/>
-      <c r="I52" s="90"/>
-      <c r="J52" s="88"/>
-      <c r="K52" s="91"/>
-      <c r="L52" s="91"/>
-      <c r="M52" s="92"/>
-      <c r="N52" s="93"/>
-      <c r="O52" s="94"/>
-      <c r="P52" s="95"/>
-      <c r="Q52" s="93"/>
-      <c r="R52" s="93"/>
+      <c r="B52" s="81"/>
+      <c r="C52" s="82"/>
+      <c r="D52" s="83"/>
+      <c r="E52" s="92"/>
+      <c r="F52" s="85"/>
+      <c r="G52" s="85"/>
+      <c r="H52" s="86"/>
+      <c r="I52" s="87"/>
+      <c r="J52" s="85"/>
+      <c r="K52" s="88"/>
+      <c r="L52" s="88"/>
+      <c r="M52" s="89"/>
+      <c r="N52" s="60"/>
+      <c r="O52" s="90"/>
+      <c r="P52" s="91"/>
+      <c r="Q52" s="60"/>
+      <c r="R52" s="60"/>
     </row>
     <row r="53" spans="1:18" ht="15" x14ac:dyDescent="0.2">
       <c r="A53" s="59"/>
-      <c r="B53" s="84"/>
-      <c r="C53" s="85"/>
-      <c r="D53" s="86"/>
-      <c r="E53" s="87"/>
-      <c r="F53" s="88"/>
-      <c r="G53" s="88"/>
-      <c r="H53" s="89"/>
-      <c r="I53" s="90"/>
-      <c r="J53" s="88"/>
-      <c r="K53" s="91"/>
-      <c r="L53" s="91"/>
-      <c r="M53" s="92"/>
-      <c r="N53" s="93"/>
-      <c r="O53" s="94"/>
-      <c r="P53" s="95"/>
-      <c r="Q53" s="93"/>
-      <c r="R53" s="93"/>
+      <c r="B53" s="81"/>
+      <c r="C53" s="82"/>
+      <c r="D53" s="83"/>
+      <c r="E53" s="84"/>
+      <c r="F53" s="85"/>
+      <c r="G53" s="85"/>
+      <c r="H53" s="86"/>
+      <c r="I53" s="87"/>
+      <c r="J53" s="85"/>
+      <c r="K53" s="88"/>
+      <c r="L53" s="88"/>
+      <c r="M53" s="89"/>
+      <c r="N53" s="60"/>
+      <c r="O53" s="90"/>
+      <c r="P53" s="91"/>
+      <c r="Q53" s="60"/>
+      <c r="R53" s="60"/>
     </row>
     <row r="54" spans="1:18" ht="15" x14ac:dyDescent="0.2">
       <c r="A54" s="59"/>
-      <c r="B54" s="84"/>
-      <c r="C54" s="85"/>
-      <c r="D54" s="86"/>
-      <c r="E54" s="87"/>
-      <c r="F54" s="88"/>
-      <c r="G54" s="88"/>
-      <c r="H54" s="89"/>
-      <c r="I54" s="90"/>
-      <c r="J54" s="88"/>
-      <c r="K54" s="91"/>
-      <c r="L54" s="91"/>
-      <c r="M54" s="92"/>
-      <c r="N54" s="93"/>
-      <c r="O54" s="94"/>
-      <c r="P54" s="95"/>
-      <c r="Q54" s="93"/>
-      <c r="R54" s="93"/>
+      <c r="B54" s="81"/>
+      <c r="C54" s="82"/>
+      <c r="D54" s="83"/>
+      <c r="E54" s="84"/>
+      <c r="F54" s="85"/>
+      <c r="G54" s="85"/>
+      <c r="H54" s="86"/>
+      <c r="I54" s="87"/>
+      <c r="J54" s="85"/>
+      <c r="K54" s="88"/>
+      <c r="L54" s="88"/>
+      <c r="M54" s="89"/>
+      <c r="N54" s="60"/>
+      <c r="O54" s="90"/>
+      <c r="P54" s="91"/>
+      <c r="Q54" s="60"/>
+      <c r="R54" s="60"/>
     </row>
     <row r="55" spans="1:18" ht="15" x14ac:dyDescent="0.2">
       <c r="A55" s="59"/>
-      <c r="B55" s="84"/>
-      <c r="C55" s="85"/>
-      <c r="D55" s="86"/>
-      <c r="E55" s="87"/>
-      <c r="F55" s="88"/>
-      <c r="G55" s="88"/>
-      <c r="H55" s="89"/>
-      <c r="I55" s="90"/>
-      <c r="J55" s="88"/>
-      <c r="K55" s="91"/>
-      <c r="L55" s="91"/>
-      <c r="M55" s="92"/>
-      <c r="N55" s="93"/>
-      <c r="O55" s="94"/>
-      <c r="P55" s="95"/>
-      <c r="Q55" s="93"/>
-      <c r="R55" s="93"/>
+      <c r="B55" s="81"/>
+      <c r="C55" s="82"/>
+      <c r="D55" s="83"/>
+      <c r="E55" s="84"/>
+      <c r="F55" s="85"/>
+      <c r="G55" s="85"/>
+      <c r="H55" s="86"/>
+      <c r="I55" s="87"/>
+      <c r="J55" s="85"/>
+      <c r="K55" s="88"/>
+      <c r="L55" s="88"/>
+      <c r="M55" s="89"/>
+      <c r="N55" s="60"/>
+      <c r="O55" s="90"/>
+      <c r="P55" s="91"/>
+      <c r="Q55" s="60"/>
+      <c r="R55" s="60"/>
     </row>
     <row r="56" spans="1:18" ht="15" x14ac:dyDescent="0.2">
       <c r="A56" s="59"/>
-      <c r="B56" s="84"/>
-      <c r="C56" s="85"/>
-      <c r="D56" s="86"/>
-      <c r="E56" s="87"/>
-      <c r="F56" s="88"/>
-      <c r="G56" s="88"/>
-      <c r="H56" s="89"/>
-      <c r="I56" s="90"/>
-      <c r="J56" s="88"/>
-      <c r="K56" s="91"/>
-      <c r="L56" s="91"/>
-      <c r="M56" s="92"/>
-      <c r="N56" s="93"/>
-      <c r="O56" s="94"/>
-      <c r="P56" s="95"/>
-      <c r="Q56" s="93"/>
-      <c r="R56" s="93"/>
+      <c r="B56" s="81"/>
+      <c r="C56" s="82"/>
+      <c r="D56" s="83"/>
+      <c r="E56" s="84"/>
+      <c r="F56" s="85"/>
+      <c r="G56" s="85"/>
+      <c r="H56" s="86"/>
+      <c r="I56" s="87"/>
+      <c r="J56" s="85" t="s">
+        <v>101</v>
+      </c>
+      <c r="K56" s="88">
+        <f>(K22+K18+K11+K2)/4</f>
+        <v>520.06784150093358</v>
+      </c>
+      <c r="L56" s="88"/>
+      <c r="M56" s="89"/>
+      <c r="N56" s="60"/>
+      <c r="O56" s="90"/>
+      <c r="P56" s="91"/>
+      <c r="Q56" s="60"/>
+      <c r="R56" s="60"/>
     </row>
     <row r="57" spans="1:18" ht="15" x14ac:dyDescent="0.2">
       <c r="A57" s="59"/>
-      <c r="B57" s="84"/>
-      <c r="C57" s="85"/>
-      <c r="D57" s="86"/>
-      <c r="E57" s="87"/>
-      <c r="F57" s="88"/>
-      <c r="G57" s="88"/>
-      <c r="H57" s="89"/>
-      <c r="I57" s="90"/>
-      <c r="J57" s="88"/>
-      <c r="K57" s="91"/>
-      <c r="L57" s="91"/>
-      <c r="M57" s="92"/>
-      <c r="N57" s="93"/>
-      <c r="O57" s="94"/>
-      <c r="P57" s="95"/>
-      <c r="Q57" s="93"/>
-      <c r="R57" s="93"/>
+      <c r="B57" s="81"/>
+      <c r="C57" s="82"/>
+      <c r="D57" s="83"/>
+      <c r="E57" s="84"/>
+      <c r="F57" s="85"/>
+      <c r="G57" s="85"/>
+      <c r="H57" s="86"/>
+      <c r="I57" s="87"/>
+      <c r="J57" s="85"/>
+      <c r="K57" s="88"/>
+      <c r="L57" s="88"/>
+      <c r="M57" s="89"/>
+      <c r="N57" s="60"/>
+      <c r="O57" s="90"/>
+      <c r="P57" s="91"/>
+      <c r="Q57" s="60"/>
+      <c r="R57" s="60"/>
     </row>
     <row r="58" spans="1:18" ht="15" x14ac:dyDescent="0.2">
       <c r="A58" s="59"/>
-      <c r="B58" s="84"/>
-      <c r="C58" s="85"/>
-      <c r="D58" s="86"/>
-      <c r="E58" s="87"/>
-      <c r="F58" s="88"/>
-      <c r="G58" s="88"/>
-      <c r="H58" s="89"/>
-      <c r="I58" s="90"/>
-      <c r="J58" s="88"/>
-      <c r="K58" s="91"/>
-      <c r="L58" s="91"/>
-      <c r="M58" s="92"/>
-      <c r="N58" s="93"/>
-      <c r="O58" s="94"/>
-      <c r="P58" s="95"/>
-      <c r="Q58" s="93"/>
-      <c r="R58" s="93"/>
+      <c r="B58" s="81"/>
+      <c r="C58" s="82"/>
+      <c r="D58" s="83"/>
+      <c r="E58" s="84"/>
+      <c r="F58" s="85"/>
+      <c r="G58" s="85"/>
+      <c r="H58" s="86"/>
+      <c r="I58" s="87"/>
+      <c r="J58" s="85"/>
+      <c r="K58" s="88"/>
+      <c r="L58" s="88"/>
+      <c r="M58" s="89"/>
+      <c r="N58" s="60"/>
+      <c r="O58" s="90"/>
+      <c r="P58" s="91"/>
+      <c r="Q58" s="60"/>
+      <c r="R58" s="60"/>
     </row>
     <row r="59" spans="1:18" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="54" t="s">
@@ -4577,7 +4741,7 @@
         <v>246.70021250000002</v>
       </c>
       <c r="J65" s="7">
-        <f t="shared" ref="J65:J67" si="40">I65+G65</f>
+        <f t="shared" ref="J65:J67" si="49">I65+G65</f>
         <v>3369.4877125000003</v>
       </c>
       <c r="K65" s="7">
@@ -4604,18 +4768,18 @@
         <v>7.75</v>
       </c>
       <c r="G66" s="7">
-        <f t="shared" ref="G66:G68" si="41">E66*F66</f>
+        <f t="shared" ref="G66:G68" si="50">E66*F66</f>
         <v>3884.6875</v>
       </c>
       <c r="H66" s="79">
         <v>5.67E-2</v>
       </c>
       <c r="I66" s="78">
-        <f t="shared" ref="I66:I67" si="42">E66*F66*H66</f>
+        <f t="shared" ref="I66:I67" si="51">E66*F66*H66</f>
         <v>220.26178125000001</v>
       </c>
       <c r="J66" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="49"/>
         <v>4104.9492812500002</v>
       </c>
       <c r="K66" s="7">
@@ -4642,18 +4806,18 @@
         <v>7.57</v>
       </c>
       <c r="G67" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="50"/>
         <v>3794.4625000000001</v>
       </c>
       <c r="H67" s="79">
         <v>5.67E-2</v>
       </c>
       <c r="I67" s="78">
-        <f t="shared" si="42"/>
+        <f t="shared" si="51"/>
         <v>215.14602375000001</v>
       </c>
       <c r="J67" s="7">
-        <f t="shared" si="40"/>
+        <f t="shared" si="49"/>
         <v>4009.6085237500001</v>
       </c>
       <c r="K67" s="7">
@@ -4680,7 +4844,7 @@
         <v>20</v>
       </c>
       <c r="G68">
-        <f t="shared" si="41"/>
+        <f t="shared" si="50"/>
         <v>10825</v>
       </c>
       <c r="I68">
@@ -4994,10 +5158,10 @@
       <c r="G7" s="40"/>
       <c r="H7" s="40"/>
       <c r="I7" s="40"/>
-      <c r="J7" s="83" t="s">
+      <c r="J7" s="95" t="s">
         <v>3</v>
       </c>
-      <c r="K7" s="83"/>
+      <c r="K7" s="95"/>
       <c r="L7" s="40"/>
       <c r="M7" s="40"/>
       <c r="N7" s="40"/>
@@ -6327,8 +6491,8 @@
       <c r="A32" s="3"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
-      <c r="D32" s="81"/>
-      <c r="E32" s="82"/>
+      <c r="D32" s="93"/>
+      <c r="E32" s="94"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
@@ -6349,8 +6513,8 @@
       <c r="A33" s="3"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="81"/>
-      <c r="E33" s="82"/>
+      <c r="D33" s="93"/>
+      <c r="E33" s="94"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
@@ -6371,8 +6535,8 @@
       <c r="A34" s="3"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
-      <c r="D34" s="81"/>
-      <c r="E34" s="82"/>
+      <c r="D34" s="93"/>
+      <c r="E34" s="94"/>
       <c r="F34" s="46"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
@@ -6393,8 +6557,8 @@
       <c r="A35" s="3"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
-      <c r="D35" s="81"/>
-      <c r="E35" s="82"/>
+      <c r="D35" s="93"/>
+      <c r="E35" s="94"/>
       <c r="F35" s="2"/>
       <c r="G35" s="29"/>
       <c r="H35" s="29"/>
@@ -6549,7 +6713,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09126FB3-8392-4E9B-BF64-082F439CA7EC}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF62BEAD-1681-4AED-B845-CC70A47A400A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
